--- a/docs/3DSA_Acompanhamento_CampusApp.xlsx
+++ b/docs/3DSA_Acompanhamento_CampusApp.xlsx
@@ -1,31 +1,47 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\.github\docs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89E220B5-64FE-43A2-B4B4-0E487E2E47DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="AvisaIF" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="IFinancas" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="iHelp" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="IFala" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="StudyDev" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="MonitoraIF" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
+    <sheet name="AvisaIF" sheetId="2" r:id="rId2"/>
+    <sheet name="IFinancas" sheetId="3" r:id="rId3"/>
+    <sheet name="iHelp" sheetId="4" r:id="rId4"/>
+    <sheet name="IFala" sheetId="5" r:id="rId5"/>
+    <sheet name="StudyDev" sheetId="6" r:id="rId6"/>
+    <sheet name="MonitoraIF" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">AvisaIF!$A$1:$I$27</definedName>
-    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">IFala!$A$1:$I$24</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">IFinancas!$A$1:$I$25</definedName>
-    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">iHelp!$A$1:$I$21</definedName>
-    <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">MonitoraIF!$A$1:$I$20</definedName>
-    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">StudyDev!$A$1:$I$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">AvisaIF!$A$1:$I$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">IFala!$A$1:$I$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">IFinancas!$A$1:$I$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">iHelp!$A$1:$I$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">MonitoraIF!$A$1:$I$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">StudyDev!$A$1:$I$24</definedName>
   </definedNames>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -36,1066 +52,1061 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="350">
   <si>
-    <t xml:space="preserve">Campus App 2025 — Painel de Acompanhamento (Turma 3DS-A)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desenvolvimento de Dispositivos Móveis · IFTM Campus Uberlândia · Prof. Edson Angoti Júnior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Equipe / Projeto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integrantes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total de cards</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feito</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fazendo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Em Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Fazer / Backlog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% Concluído</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aulas estimadas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aulas concluídas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avisa IF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rebeca, Adan, Alejandro, Enzo Eduardo, Enzo Leonardo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFinanças</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Davi Gonzaga, Gabelo, Gabriel Almeida, Vinicius Mendes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iHelp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caio Gabriel, Vitória Sophia, Camille, Iago Borges, Daniel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFala</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clara Lindemann, Davi Rodovalho, Enzo Ribeiro, Lucas Mercado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">StudyDev</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iago Oliveira, Nicolas Bruno, Felipe Peixoto, Felipe Marques, Heitor Moreira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MonitoraIF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heitor Leal, Gabriel Zumba, Otávio Rodrigues, João Lucas Sivieri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOTAL DA TURMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Como usar:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Cada equipe tem uma aba com todos os cards (mesmos IDs dos arquivos 3DSA_Kanban_*.md).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. Atualize só as colunas Status e Responsável nas abas — o Dashboard recalcula sozinho.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Status: Backlog · A Fazer · Fazendo · Em Review · Feito (lista suspensa na célula).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. Sprint: 1 = Sem. 5–6 · 2 = Sem. 7–8 · 3 = Sem. 9–10.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5. Estimativas em aulas (1 aula ≈ 50 min). Aulas concluídas somam só cards com status Feito.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Issue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Card (atividade)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prioridade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Est. (aulas)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Responsável</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observações</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVI-01.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVI-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Criar projeto Firebase e ativar Auth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Fazer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVI-01.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UI das telas de Login e Cadastro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVI-01.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integrar cadastro/login com Firebase Auth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVI-01.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AuthContext + navegação + persistência</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVI-02.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVI-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coleção usuarios com campo papel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVI-02.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expor papel no AuthContext</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVI-02.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Header com aviso da semana (só grêmio)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVI-03.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVI-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modelar coleção grupos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Backlog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVI-03.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UI criar grupo (nome + cor + código)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVI-03.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UI entrar via código</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVI-03.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Componente CardGrupo colorido</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVI-04.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVI-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FlatList dos grupos do usuário</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVI-04.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Botão + criar/entrar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVI-05.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVI-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UI formulário de aviso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVI-05.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gravar aviso na subcoleção do grupo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVI-06.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVI-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Query dos avisos de todos os grupos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVI-06.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agenda agrupada por dia com cor do grupo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVI-06.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Separar futuros e passados</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVI-07.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVI-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marcar aviso como concluído (pessoal)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVI-07.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estilo atenuado p/ concluídos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVI-08.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVI-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chips de grupo na agenda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVI-09.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVI-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">expo-notifications + permissão</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVI-09.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notificação 1 dia antes do aviso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVI-10.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVI-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Animações de transição</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVI-QA.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teste cruzado + registro de bugs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVI-QA.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corrigir bugs priorizados</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total de aulas estimadas:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aulas concluídas (Feito):</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFI-01.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFI-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFI-01.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFI-01.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFI-01.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AuthContext + persistência + regras por UID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFI-02.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFI-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modelar coleção transacoes/{uid}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFI-02.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UI formulário de gasto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFI-02.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gravar gasto no Firestore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFI-03.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFI-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contexto (escola/fora) + categoria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFI-03.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dashboard separa totais por contexto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFI-04.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFI-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FlatList ordenada por data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFI-04.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remover transação com confirmação</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFI-05.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFI-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calcular totais do mês</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFI-05.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cartões informativos no painel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFI-05.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Atualização automática</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFI-06.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFI-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avaliar/decidir lib de gráfico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFI-06.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gráfico por categoria com legenda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFI-07.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFI-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Definir limite mensal no perfil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFI-07.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aviso ao ultrapassar limite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFI-08.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFI-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cadastro de meta (valor + prazo)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFI-08.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barra de progresso da meta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFI-09.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFI-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seletor de mês/ano</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFI-09.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resumo do mês selecionado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFI-QA.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFI-QA.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IHP-01.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IHP-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IHP-01.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UI Login/Cadastro com seleção de tipo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IHP-01.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integrar Auth + coleção usuarios com tipo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IHP-01.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IHP-02.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IHP-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modelar coleção prestadores</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IHP-02.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UI formulário de perfil profissional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IHP-02.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gravar/editar perfil no Firestore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IHP-03.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IHP-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Componente CardPrestador</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IHP-03.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FlatList carregando do Firestore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IHP-04.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IHP-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UI da tela de detalhe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IHP-04.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contato via deep link</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IHP-05.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IHP-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Definir lista de categorias</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IHP-05.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tela inicial com categorias</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IHP-06.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IHP-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tela de edição do perfil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IHP-07.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IHP-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avaliação 1–5 estrelas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IHP-07.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Média no card e no detalhe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IHP-08.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IHP-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barra de pesquisa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IHP-09.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IHP-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filtro por categoria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IHP-QA.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IHP-QA.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFA-01.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFA-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFA-01.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFA-01.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integrar Auth + validação de domínio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFA-01.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AuthContext + persistência</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFA-02.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFA-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coleção usuarios com papel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFA-02.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navegação condicional por papel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFA-03.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFA-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modelar coleção reclamacoes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFA-03.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UI formulário (categoria + texto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFA-03.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gravar com status aberta + confirmação</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFA-04.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFA-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regras Firestore ocultam autorUid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFA-04.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Texto de transparência (privacidade)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFA-05.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFA-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lista das próprias reclamações</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFA-05.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Detalhe com resposta da coordenação</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFA-06.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFA-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Painel sem identificação do autor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFA-06.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abrir detalhe para análise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFA-07.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFA-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campo de resposta + mudança de status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFA-07.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resposta reflete via onSnapshot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFA-08.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFA-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filtrar por categoria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFA-09.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFA-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anexar evidência (foto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFA-09.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Imagem no detalhe sem expor autor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFA-QA.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFA-QA.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFA-QA.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revisar proteção do autor (cenário real)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STD-01.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STD-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STD-01.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STD-01.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integrar Auth + AuthContext + persistência</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STD-02.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STD-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Documentar schema de progresso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STD-02.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Criar progresso/{uid} + hook useProgresso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STD-03.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STD-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schema da aula + 1 aula-modelo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STD-03.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Escrever trilha 1 (3 mód × 3 aulas)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STD-03.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Escrever trilha 2 (3 mód × 3 aulas)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STD-03.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carregar trilhas no Firestore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STD-04.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STD-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Componente CardTrilha com progresso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STD-04.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grid de trilhas (Firestore)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STD-05.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STD-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aulas agrupadas por módulo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STD-05.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navegação aula → conteúdo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STD-06.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STD-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UI do conteúdo (texto + vídeo opcional)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STD-06.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marcar como concluída + progresso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STD-07.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STD-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contador de streak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STD-07.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mensagem motivacional diária</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STD-08.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STD-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STD-08.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lembrete diário em horário escolhido</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STD-09.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STD-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modo escuro (ThemeContext)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STD-QA.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STD-QA.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STD-QA.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revisão de conteúdo das trilhas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIF-01.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIF-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIF-01.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIF-01.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIF-02.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIF-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coleção usuarios com papel + seleção</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIF-02.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expor papel + permissões</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIF-03.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIF-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modelar coleção duvidas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIF-03.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UI formulário (matéria, título, descrição)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIF-03.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gravar dúvida com status aberta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIF-04.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIF-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Componente CardDuvida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIF-04.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FlatList com onSnapshot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIF-05.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIF-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UI do detalhe (dúvida + respostas)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIF-06.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIF-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subcoleção respostas + campo (só monitor)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIF-06.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Respostas em tempo real + status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIF-07.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIF-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Botão Resolvida (só autor)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIF-08.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIF-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitor cadastra horários</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIF-08.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aluno visualiza horários</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIF-09.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIF-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filtrar dúvidas por matéria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIF-QA.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIF-QA.2</t>
+    <t>Campus App 2025 — Painel de Acompanhamento (Turma 3DS-A)</t>
+  </si>
+  <si>
+    <t>Desenvolvimento de Dispositivos Móveis · IFTM Campus Uberlândia · Prof. Edson Angoti Júnior</t>
+  </si>
+  <si>
+    <t>Equipe / Projeto</t>
+  </si>
+  <si>
+    <t>Integrantes</t>
+  </si>
+  <si>
+    <t>Total de cards</t>
+  </si>
+  <si>
+    <t>Feito</t>
+  </si>
+  <si>
+    <t>Fazendo</t>
+  </si>
+  <si>
+    <t>Em Review</t>
+  </si>
+  <si>
+    <t>A Fazer / Backlog</t>
+  </si>
+  <si>
+    <t>% Concluído</t>
+  </si>
+  <si>
+    <t>Aulas estimadas</t>
+  </si>
+  <si>
+    <t>Aulas concluídas</t>
+  </si>
+  <si>
+    <t>Avisa IF</t>
+  </si>
+  <si>
+    <t>Rebeca, Adan, Alejandro, Enzo Eduardo, Enzo Leonardo</t>
+  </si>
+  <si>
+    <t>IFinanças</t>
+  </si>
+  <si>
+    <t>Davi Gonzaga, Gabelo, Gabriel Almeida, Vinicius Mendes</t>
+  </si>
+  <si>
+    <t>iHelp</t>
+  </si>
+  <si>
+    <t>Caio Gabriel, Vitória Sophia, Camille, Iago Borges, Daniel</t>
+  </si>
+  <si>
+    <t>IFala</t>
+  </si>
+  <si>
+    <t>Clara Lindemann, Davi Rodovalho, Enzo Ribeiro, Lucas Mercado</t>
+  </si>
+  <si>
+    <t>StudyDev</t>
+  </si>
+  <si>
+    <t>Iago Oliveira, Nicolas Bruno, Felipe Peixoto, Felipe Marques, Heitor Moreira</t>
+  </si>
+  <si>
+    <t>MonitoraIF</t>
+  </si>
+  <si>
+    <t>Heitor Leal, Gabriel Zumba, Otávio Rodrigues, João Lucas Sivieri</t>
+  </si>
+  <si>
+    <t>TOTAL DA TURMA</t>
+  </si>
+  <si>
+    <t>Como usar:</t>
+  </si>
+  <si>
+    <t>1. Cada equipe tem uma aba com todos os cards (mesmos IDs dos arquivos 3DSA_Kanban_*.md).</t>
+  </si>
+  <si>
+    <t>2. Atualize só as colunas Status e Responsável nas abas — o Dashboard recalcula sozinho.</t>
+  </si>
+  <si>
+    <t>3. Status: Backlog · A Fazer · Fazendo · Em Review · Feito (lista suspensa na célula).</t>
+  </si>
+  <si>
+    <t>4. Sprint: 1 = Sem. 5–6 · 2 = Sem. 7–8 · 3 = Sem. 9–10.</t>
+  </si>
+  <si>
+    <t>5. Estimativas em aulas (1 aula ≈ 50 min). Aulas concluídas somam só cards com status Feito.</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Issue</t>
+  </si>
+  <si>
+    <t>Card (atividade)</t>
+  </si>
+  <si>
+    <t>Prioridade</t>
+  </si>
+  <si>
+    <t>Sprint</t>
+  </si>
+  <si>
+    <t>Est. (aulas)</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Responsável</t>
+  </si>
+  <si>
+    <t>Observações</t>
+  </si>
+  <si>
+    <t>AVI-01.1</t>
+  </si>
+  <si>
+    <t>AVI-01</t>
+  </si>
+  <si>
+    <t>Criar projeto Firebase e ativar Auth</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>A Fazer</t>
+  </si>
+  <si>
+    <t>AVI-01.2</t>
+  </si>
+  <si>
+    <t>UI das telas de Login e Cadastro</t>
+  </si>
+  <si>
+    <t>AVI-01.3</t>
+  </si>
+  <si>
+    <t>Integrar cadastro/login com Firebase Auth</t>
+  </si>
+  <si>
+    <t>AVI-01.4</t>
+  </si>
+  <si>
+    <t>AuthContext + navegação + persistência</t>
+  </si>
+  <si>
+    <t>AVI-02.1</t>
+  </si>
+  <si>
+    <t>AVI-02</t>
+  </si>
+  <si>
+    <t>Coleção usuarios com campo papel</t>
+  </si>
+  <si>
+    <t>AVI-02.2</t>
+  </si>
+  <si>
+    <t>Expor papel no AuthContext</t>
+  </si>
+  <si>
+    <t>AVI-02.3</t>
+  </si>
+  <si>
+    <t>Header com aviso da semana (só grêmio)</t>
+  </si>
+  <si>
+    <t>AVI-03.1</t>
+  </si>
+  <si>
+    <t>AVI-03</t>
+  </si>
+  <si>
+    <t>Modelar coleção grupos</t>
+  </si>
+  <si>
+    <t>Backlog</t>
+  </si>
+  <si>
+    <t>AVI-03.2</t>
+  </si>
+  <si>
+    <t>UI criar grupo (nome + cor + código)</t>
+  </si>
+  <si>
+    <t>AVI-03.3</t>
+  </si>
+  <si>
+    <t>UI entrar via código</t>
+  </si>
+  <si>
+    <t>AVI-03.4</t>
+  </si>
+  <si>
+    <t>Componente CardGrupo colorido</t>
+  </si>
+  <si>
+    <t>AVI-04.1</t>
+  </si>
+  <si>
+    <t>AVI-04</t>
+  </si>
+  <si>
+    <t>FlatList dos grupos do usuário</t>
+  </si>
+  <si>
+    <t>AVI-04.2</t>
+  </si>
+  <si>
+    <t>Botão + criar/entrar</t>
+  </si>
+  <si>
+    <t>AVI-05.1</t>
+  </si>
+  <si>
+    <t>AVI-05</t>
+  </si>
+  <si>
+    <t>UI formulário de aviso</t>
+  </si>
+  <si>
+    <t>AVI-05.2</t>
+  </si>
+  <si>
+    <t>Gravar aviso na subcoleção do grupo</t>
+  </si>
+  <si>
+    <t>AVI-06.1</t>
+  </si>
+  <si>
+    <t>AVI-06</t>
+  </si>
+  <si>
+    <t>Query dos avisos de todos os grupos</t>
+  </si>
+  <si>
+    <t>AVI-06.2</t>
+  </si>
+  <si>
+    <t>Agenda agrupada por dia com cor do grupo</t>
+  </si>
+  <si>
+    <t>AVI-06.3</t>
+  </si>
+  <si>
+    <t>Separar futuros e passados</t>
+  </si>
+  <si>
+    <t>AVI-07.1</t>
+  </si>
+  <si>
+    <t>AVI-07</t>
+  </si>
+  <si>
+    <t>Marcar aviso como concluído (pessoal)</t>
+  </si>
+  <si>
+    <t>AVI-07.2</t>
+  </si>
+  <si>
+    <t>Estilo atenuado p/ concluídos</t>
+  </si>
+  <si>
+    <t>AVI-08.1</t>
+  </si>
+  <si>
+    <t>AVI-08</t>
+  </si>
+  <si>
+    <t>Chips de grupo na agenda</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>AVI-09.1</t>
+  </si>
+  <si>
+    <t>AVI-09</t>
+  </si>
+  <si>
+    <t>expo-notifications + permissão</t>
+  </si>
+  <si>
+    <t>AVI-09.2</t>
+  </si>
+  <si>
+    <t>Notificação 1 dia antes do aviso</t>
+  </si>
+  <si>
+    <t>AVI-10.1</t>
+  </si>
+  <si>
+    <t>AVI-10</t>
+  </si>
+  <si>
+    <t>Animações de transição</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>AVI-QA.1</t>
+  </si>
+  <si>
+    <t>QA</t>
+  </si>
+  <si>
+    <t>Teste cruzado + registro de bugs</t>
+  </si>
+  <si>
+    <t>AVI-QA.2</t>
+  </si>
+  <si>
+    <t>Corrigir bugs priorizados</t>
+  </si>
+  <si>
+    <t>Total de aulas estimadas:</t>
+  </si>
+  <si>
+    <t>Aulas concluídas (Feito):</t>
+  </si>
+  <si>
+    <t>IFI-01.1</t>
+  </si>
+  <si>
+    <t>IFI-01</t>
+  </si>
+  <si>
+    <t>IFI-01.2</t>
+  </si>
+  <si>
+    <t>IFI-01.3</t>
+  </si>
+  <si>
+    <t>IFI-01.4</t>
+  </si>
+  <si>
+    <t>AuthContext + persistência + regras por UID</t>
+  </si>
+  <si>
+    <t>IFI-02.1</t>
+  </si>
+  <si>
+    <t>IFI-02</t>
+  </si>
+  <si>
+    <t>Modelar coleção transacoes/{uid}</t>
+  </si>
+  <si>
+    <t>IFI-02.2</t>
+  </si>
+  <si>
+    <t>UI formulário de gasto</t>
+  </si>
+  <si>
+    <t>IFI-02.3</t>
+  </si>
+  <si>
+    <t>Gravar gasto no Firestore</t>
+  </si>
+  <si>
+    <t>IFI-03.1</t>
+  </si>
+  <si>
+    <t>IFI-03</t>
+  </si>
+  <si>
+    <t>Contexto (escola/fora) + categoria</t>
+  </si>
+  <si>
+    <t>IFI-03.2</t>
+  </si>
+  <si>
+    <t>Dashboard separa totais por contexto</t>
+  </si>
+  <si>
+    <t>IFI-04.1</t>
+  </si>
+  <si>
+    <t>IFI-04</t>
+  </si>
+  <si>
+    <t>FlatList ordenada por data</t>
+  </si>
+  <si>
+    <t>IFI-04.2</t>
+  </si>
+  <si>
+    <t>Remover transação com confirmação</t>
+  </si>
+  <si>
+    <t>IFI-05.1</t>
+  </si>
+  <si>
+    <t>IFI-05</t>
+  </si>
+  <si>
+    <t>Calcular totais do mês</t>
+  </si>
+  <si>
+    <t>IFI-05.2</t>
+  </si>
+  <si>
+    <t>Cartões informativos no painel</t>
+  </si>
+  <si>
+    <t>IFI-05.3</t>
+  </si>
+  <si>
+    <t>Atualização automática</t>
+  </si>
+  <si>
+    <t>IFI-06.1</t>
+  </si>
+  <si>
+    <t>IFI-06</t>
+  </si>
+  <si>
+    <t>Avaliar/decidir lib de gráfico</t>
+  </si>
+  <si>
+    <t>IFI-06.2</t>
+  </si>
+  <si>
+    <t>Gráfico por categoria com legenda</t>
+  </si>
+  <si>
+    <t>IFI-07.1</t>
+  </si>
+  <si>
+    <t>IFI-07</t>
+  </si>
+  <si>
+    <t>Definir limite mensal no perfil</t>
+  </si>
+  <si>
+    <t>IFI-07.2</t>
+  </si>
+  <si>
+    <t>Aviso ao ultrapassar limite</t>
+  </si>
+  <si>
+    <t>IFI-08.1</t>
+  </si>
+  <si>
+    <t>IFI-08</t>
+  </si>
+  <si>
+    <t>Cadastro de meta (valor + prazo)</t>
+  </si>
+  <si>
+    <t>IFI-08.2</t>
+  </si>
+  <si>
+    <t>Barra de progresso da meta</t>
+  </si>
+  <si>
+    <t>IFI-09.1</t>
+  </si>
+  <si>
+    <t>IFI-09</t>
+  </si>
+  <si>
+    <t>Seletor de mês/ano</t>
+  </si>
+  <si>
+    <t>IFI-09.2</t>
+  </si>
+  <si>
+    <t>Resumo do mês selecionado</t>
+  </si>
+  <si>
+    <t>IFI-QA.1</t>
+  </si>
+  <si>
+    <t>IFI-QA.2</t>
+  </si>
+  <si>
+    <t>IHP-01.1</t>
+  </si>
+  <si>
+    <t>IHP-01</t>
+  </si>
+  <si>
+    <t>IHP-01.2</t>
+  </si>
+  <si>
+    <t>UI Login/Cadastro com seleção de tipo</t>
+  </si>
+  <si>
+    <t>IHP-01.3</t>
+  </si>
+  <si>
+    <t>Integrar Auth + coleção usuarios com tipo</t>
+  </si>
+  <si>
+    <t>IHP-01.4</t>
+  </si>
+  <si>
+    <t>IHP-02.1</t>
+  </si>
+  <si>
+    <t>IHP-02</t>
+  </si>
+  <si>
+    <t>Modelar coleção prestadores</t>
+  </si>
+  <si>
+    <t>IHP-02.2</t>
+  </si>
+  <si>
+    <t>UI formulário de perfil profissional</t>
+  </si>
+  <si>
+    <t>IHP-02.3</t>
+  </si>
+  <si>
+    <t>Gravar/editar perfil no Firestore</t>
+  </si>
+  <si>
+    <t>IHP-03.1</t>
+  </si>
+  <si>
+    <t>IHP-03</t>
+  </si>
+  <si>
+    <t>Componente CardPrestador</t>
+  </si>
+  <si>
+    <t>IHP-03.2</t>
+  </si>
+  <si>
+    <t>FlatList carregando do Firestore</t>
+  </si>
+  <si>
+    <t>IHP-04.1</t>
+  </si>
+  <si>
+    <t>IHP-04</t>
+  </si>
+  <si>
+    <t>UI da tela de detalhe</t>
+  </si>
+  <si>
+    <t>IHP-04.2</t>
+  </si>
+  <si>
+    <t>Contato via deep link</t>
+  </si>
+  <si>
+    <t>IHP-05.1</t>
+  </si>
+  <si>
+    <t>IHP-05</t>
+  </si>
+  <si>
+    <t>Definir lista de categorias</t>
+  </si>
+  <si>
+    <t>IHP-05.2</t>
+  </si>
+  <si>
+    <t>Tela inicial com categorias</t>
+  </si>
+  <si>
+    <t>IHP-06.1</t>
+  </si>
+  <si>
+    <t>IHP-06</t>
+  </si>
+  <si>
+    <t>Tela de edição do perfil</t>
+  </si>
+  <si>
+    <t>IHP-07.1</t>
+  </si>
+  <si>
+    <t>IHP-07</t>
+  </si>
+  <si>
+    <t>Avaliação 1–5 estrelas</t>
+  </si>
+  <si>
+    <t>IHP-07.2</t>
+  </si>
+  <si>
+    <t>Média no card e no detalhe</t>
+  </si>
+  <si>
+    <t>IHP-08.1</t>
+  </si>
+  <si>
+    <t>IHP-08</t>
+  </si>
+  <si>
+    <t>Barra de pesquisa</t>
+  </si>
+  <si>
+    <t>IHP-09.1</t>
+  </si>
+  <si>
+    <t>IHP-09</t>
+  </si>
+  <si>
+    <t>Filtro por categoria</t>
+  </si>
+  <si>
+    <t>IHP-QA.1</t>
+  </si>
+  <si>
+    <t>IHP-QA.2</t>
+  </si>
+  <si>
+    <t>IFA-01.1</t>
+  </si>
+  <si>
+    <t>IFA-01</t>
+  </si>
+  <si>
+    <t>IFA-01.2</t>
+  </si>
+  <si>
+    <t>IFA-01.3</t>
+  </si>
+  <si>
+    <t>Integrar Auth + validação de domínio</t>
+  </si>
+  <si>
+    <t>IFA-01.4</t>
+  </si>
+  <si>
+    <t>AuthContext + persistência</t>
+  </si>
+  <si>
+    <t>IFA-02.1</t>
+  </si>
+  <si>
+    <t>IFA-02</t>
+  </si>
+  <si>
+    <t>Coleção usuarios com papel</t>
+  </si>
+  <si>
+    <t>IFA-02.2</t>
+  </si>
+  <si>
+    <t>Navegação condicional por papel</t>
+  </si>
+  <si>
+    <t>IFA-03.1</t>
+  </si>
+  <si>
+    <t>IFA-03</t>
+  </si>
+  <si>
+    <t>Modelar coleção reclamacoes</t>
+  </si>
+  <si>
+    <t>IFA-03.2</t>
+  </si>
+  <si>
+    <t>UI formulário (categoria + texto)</t>
+  </si>
+  <si>
+    <t>IFA-03.3</t>
+  </si>
+  <si>
+    <t>Gravar com status aberta + confirmação</t>
+  </si>
+  <si>
+    <t>IFA-04.1</t>
+  </si>
+  <si>
+    <t>IFA-04</t>
+  </si>
+  <si>
+    <t>Regras Firestore ocultam autorUid</t>
+  </si>
+  <si>
+    <t>IFA-04.2</t>
+  </si>
+  <si>
+    <t>Texto de transparência (privacidade)</t>
+  </si>
+  <si>
+    <t>IFA-05.1</t>
+  </si>
+  <si>
+    <t>IFA-05</t>
+  </si>
+  <si>
+    <t>Lista das próprias reclamações</t>
+  </si>
+  <si>
+    <t>IFA-05.2</t>
+  </si>
+  <si>
+    <t>Detalhe com resposta da coordenação</t>
+  </si>
+  <si>
+    <t>IFA-06.1</t>
+  </si>
+  <si>
+    <t>IFA-06</t>
+  </si>
+  <si>
+    <t>Painel sem identificação do autor</t>
+  </si>
+  <si>
+    <t>IFA-06.2</t>
+  </si>
+  <si>
+    <t>Abrir detalhe para análise</t>
+  </si>
+  <si>
+    <t>IFA-07.1</t>
+  </si>
+  <si>
+    <t>IFA-07</t>
+  </si>
+  <si>
+    <t>Campo de resposta + mudança de status</t>
+  </si>
+  <si>
+    <t>IFA-07.2</t>
+  </si>
+  <si>
+    <t>Resposta reflete via onSnapshot</t>
+  </si>
+  <si>
+    <t>IFA-08.1</t>
+  </si>
+  <si>
+    <t>IFA-08</t>
+  </si>
+  <si>
+    <t>Filtrar por categoria</t>
+  </si>
+  <si>
+    <t>IFA-09.1</t>
+  </si>
+  <si>
+    <t>IFA-09</t>
+  </si>
+  <si>
+    <t>Anexar evidência (foto)</t>
+  </si>
+  <si>
+    <t>IFA-09.2</t>
+  </si>
+  <si>
+    <t>Imagem no detalhe sem expor autor</t>
+  </si>
+  <si>
+    <t>IFA-QA.1</t>
+  </si>
+  <si>
+    <t>IFA-QA.2</t>
+  </si>
+  <si>
+    <t>IFA-QA.3</t>
+  </si>
+  <si>
+    <t>Revisar proteção do autor (cenário real)</t>
+  </si>
+  <si>
+    <t>STD-01.1</t>
+  </si>
+  <si>
+    <t>STD-01</t>
+  </si>
+  <si>
+    <t>STD-01.2</t>
+  </si>
+  <si>
+    <t>STD-01.3</t>
+  </si>
+  <si>
+    <t>Integrar Auth + AuthContext + persistência</t>
+  </si>
+  <si>
+    <t>STD-02.1</t>
+  </si>
+  <si>
+    <t>STD-02</t>
+  </si>
+  <si>
+    <t>Documentar schema de progresso</t>
+  </si>
+  <si>
+    <t>STD-02.2</t>
+  </si>
+  <si>
+    <t>Criar progresso/{uid} + hook useProgresso</t>
+  </si>
+  <si>
+    <t>STD-03.1</t>
+  </si>
+  <si>
+    <t>STD-03</t>
+  </si>
+  <si>
+    <t>Schema da aula + 1 aula-modelo</t>
+  </si>
+  <si>
+    <t>STD-03.2</t>
+  </si>
+  <si>
+    <t>Escrever trilha 1 (3 mód × 3 aulas)</t>
+  </si>
+  <si>
+    <t>STD-03.3</t>
+  </si>
+  <si>
+    <t>Escrever trilha 2 (3 mód × 3 aulas)</t>
+  </si>
+  <si>
+    <t>STD-03.4</t>
+  </si>
+  <si>
+    <t>Carregar trilhas no Firestore</t>
+  </si>
+  <si>
+    <t>STD-04.1</t>
+  </si>
+  <si>
+    <t>STD-04</t>
+  </si>
+  <si>
+    <t>Componente CardTrilha com progresso</t>
+  </si>
+  <si>
+    <t>STD-04.2</t>
+  </si>
+  <si>
+    <t>Grid de trilhas (Firestore)</t>
+  </si>
+  <si>
+    <t>STD-05.1</t>
+  </si>
+  <si>
+    <t>STD-05</t>
+  </si>
+  <si>
+    <t>Aulas agrupadas por módulo</t>
+  </si>
+  <si>
+    <t>STD-05.2</t>
+  </si>
+  <si>
+    <t>Navegação aula → conteúdo</t>
+  </si>
+  <si>
+    <t>STD-06.1</t>
+  </si>
+  <si>
+    <t>STD-06</t>
+  </si>
+  <si>
+    <t>UI do conteúdo (texto + vídeo opcional)</t>
+  </si>
+  <si>
+    <t>STD-06.2</t>
+  </si>
+  <si>
+    <t>Marcar como concluída + progresso</t>
+  </si>
+  <si>
+    <t>STD-07.1</t>
+  </si>
+  <si>
+    <t>STD-07</t>
+  </si>
+  <si>
+    <t>Contador de streak</t>
+  </si>
+  <si>
+    <t>STD-07.2</t>
+  </si>
+  <si>
+    <t>Mensagem motivacional diária</t>
+  </si>
+  <si>
+    <t>STD-08.1</t>
+  </si>
+  <si>
+    <t>STD-08</t>
+  </si>
+  <si>
+    <t>STD-08.2</t>
+  </si>
+  <si>
+    <t>Lembrete diário em horário escolhido</t>
+  </si>
+  <si>
+    <t>STD-09.1</t>
+  </si>
+  <si>
+    <t>STD-09</t>
+  </si>
+  <si>
+    <t>Modo escuro (ThemeContext)</t>
+  </si>
+  <si>
+    <t>STD-QA.1</t>
+  </si>
+  <si>
+    <t>STD-QA.2</t>
+  </si>
+  <si>
+    <t>STD-QA.3</t>
+  </si>
+  <si>
+    <t>Revisão de conteúdo das trilhas</t>
+  </si>
+  <si>
+    <t>MIF-01.1</t>
+  </si>
+  <si>
+    <t>MIF-01</t>
+  </si>
+  <si>
+    <t>MIF-01.2</t>
+  </si>
+  <si>
+    <t>MIF-01.3</t>
+  </si>
+  <si>
+    <t>MIF-02.1</t>
+  </si>
+  <si>
+    <t>MIF-02</t>
+  </si>
+  <si>
+    <t>Coleção usuarios com papel + seleção</t>
+  </si>
+  <si>
+    <t>MIF-02.2</t>
+  </si>
+  <si>
+    <t>Expor papel + permissões</t>
+  </si>
+  <si>
+    <t>MIF-03.1</t>
+  </si>
+  <si>
+    <t>MIF-03</t>
+  </si>
+  <si>
+    <t>Modelar coleção duvidas</t>
+  </si>
+  <si>
+    <t>MIF-03.2</t>
+  </si>
+  <si>
+    <t>UI formulário (matéria, título, descrição)</t>
+  </si>
+  <si>
+    <t>MIF-03.3</t>
+  </si>
+  <si>
+    <t>Gravar dúvida com status aberta</t>
+  </si>
+  <si>
+    <t>MIF-04.1</t>
+  </si>
+  <si>
+    <t>MIF-04</t>
+  </si>
+  <si>
+    <t>Componente CardDuvida</t>
+  </si>
+  <si>
+    <t>MIF-04.2</t>
+  </si>
+  <si>
+    <t>FlatList com onSnapshot</t>
+  </si>
+  <si>
+    <t>MIF-05.1</t>
+  </si>
+  <si>
+    <t>MIF-05</t>
+  </si>
+  <si>
+    <t>UI do detalhe (dúvida + respostas)</t>
+  </si>
+  <si>
+    <t>MIF-06.1</t>
+  </si>
+  <si>
+    <t>MIF-06</t>
+  </si>
+  <si>
+    <t>Subcoleção respostas + campo (só monitor)</t>
+  </si>
+  <si>
+    <t>MIF-06.2</t>
+  </si>
+  <si>
+    <t>Respostas em tempo real + status</t>
+  </si>
+  <si>
+    <t>MIF-07.1</t>
+  </si>
+  <si>
+    <t>MIF-07</t>
+  </si>
+  <si>
+    <t>Botão Resolvida (só autor)</t>
+  </si>
+  <si>
+    <t>MIF-08.1</t>
+  </si>
+  <si>
+    <t>MIF-08</t>
+  </si>
+  <si>
+    <t>Monitor cadastra horários</t>
+  </si>
+  <si>
+    <t>MIF-08.2</t>
+  </si>
+  <si>
+    <t>Aluno visualiza horários</t>
+  </si>
+  <si>
+    <t>MIF-09.1</t>
+  </si>
+  <si>
+    <t>MIF-09</t>
+  </si>
+  <si>
+    <t>Filtrar dúvidas por matéria</t>
+  </si>
+  <si>
+    <t>MIF-QA.1</t>
+  </si>
+  <si>
+    <t>MIF-QA.2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="General"/>
-    <numFmt numFmtId="166" formatCode="0%"/>
-  </numFmts>
-  <fonts count="19">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1104,135 +1115,105 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="16"/>
       <color rgb="FF1E2761"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF64748B"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FF7C3AED"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF1E293B"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FFF97316"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FF0E7490"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FF0891B2"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FF059669"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FF1E2761"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF475569"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FFDC2626"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FFCA8A04"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FF64748B"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FF1E293B"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -1311,14 +1292,14 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFCCCCCC"/>
       </left>
@@ -1334,307 +1315,108 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="34">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="36">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="9" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="9" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="9" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="15">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF7C3AED"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF1F5F9"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF1E2761"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF64748B"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF1E293B"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE2E8F0"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFEE2E2"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFEF9C3"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCA8A04"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDC2626"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF97316"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF0E7490"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF0891B2"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF059669"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -1693,71 +1475,63 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF475569"/>
       <rgbColor rgb="FF1E293B"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -1765,12 +1539,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -1799,7 +1573,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1820,7 +1594,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -1871,7 +1645,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1889,46 +1663,45 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:K19"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="15"/>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="2:11" ht="21" x14ac:dyDescent="0.4">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" spans="2:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
@@ -1960,345 +1733,337 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="2:11" ht="26.4" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="6" t="n">
-        <f aca="false">COUNTA(AvisaIF!A2:A27)</f>
+      <c r="D6" s="6">
+        <f>COUNTA(AvisaIF!A2:A27)</f>
         <v>26</v>
       </c>
-      <c r="E6" s="6" t="n">
-        <f aca="false">COUNTIF(AvisaIF!G2:G27,"Feito")</f>
+      <c r="E6" s="6">
+        <f>COUNTIF(AvisaIF!G2:G27,"Feito")</f>
         <v>0</v>
       </c>
-      <c r="F6" s="6" t="n">
-        <f aca="false">COUNTIF(AvisaIF!G2:G27,"Fazendo")</f>
+      <c r="F6" s="6">
+        <f>COUNTIF(AvisaIF!G2:G27,"Fazendo")</f>
         <v>0</v>
       </c>
-      <c r="G6" s="6" t="n">
-        <f aca="false">COUNTIF(AvisaIF!G2:G27,"Em Review")</f>
+      <c r="G6" s="6">
+        <f>COUNTIF(AvisaIF!G2:G27,"Em Review")</f>
         <v>0</v>
       </c>
-      <c r="H6" s="6" t="n">
-        <f aca="false">COUNTIF(AvisaIF!G2:G27,"A Fazer")+COUNTIF(AvisaIF!G2:G27,"Backlog")</f>
+      <c r="H6" s="6">
+        <f>COUNTIF(AvisaIF!G2:G27,"A Fazer")+COUNTIF(AvisaIF!G2:G27,"Backlog")</f>
         <v>26</v>
       </c>
-      <c r="I6" s="7" t="n">
-        <f aca="false">IF(D6=0,0,E6/D6)</f>
+      <c r="I6" s="7">
+        <f t="shared" ref="I6:I12" si="0">IF(D6=0,0,E6/D6)</f>
         <v>0</v>
       </c>
-      <c r="J6" s="6" t="n">
-        <f aca="false">SUM(AvisaIF!F2:F27)</f>
+      <c r="J6" s="6">
+        <f>SUM(AvisaIF!F2:F27)</f>
         <v>25.5</v>
       </c>
-      <c r="K6" s="6" t="n">
-        <f aca="false">SUMIF(AvisaIF!G2:G27,"Feito",AvisaIF!F2:F27)</f>
+      <c r="K6" s="6">
+        <f>SUMIF(AvisaIF!G2:G27,"Feito",AvisaIF!F2:F27)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="2:11" ht="26.4" x14ac:dyDescent="0.3">
       <c r="B7" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="10" t="n">
-        <f aca="false">COUNTA(IFinancas!A2:A25)</f>
+      <c r="D7" s="10">
+        <f>COUNTA(IFinancas!A2:A25)</f>
         <v>24</v>
       </c>
-      <c r="E7" s="10" t="n">
-        <f aca="false">COUNTIF(IFinancas!G2:G25,"Feito")</f>
+      <c r="E7" s="10">
+        <f>COUNTIF(IFinancas!G2:G25,"Feito")</f>
         <v>0</v>
       </c>
-      <c r="F7" s="10" t="n">
-        <f aca="false">COUNTIF(IFinancas!G2:G25,"Fazendo")</f>
+      <c r="F7" s="10">
+        <f>COUNTIF(IFinancas!G2:G25,"Fazendo")</f>
         <v>0</v>
       </c>
-      <c r="G7" s="10" t="n">
-        <f aca="false">COUNTIF(IFinancas!G2:G25,"Em Review")</f>
+      <c r="G7" s="10">
+        <f>COUNTIF(IFinancas!G2:G25,"Em Review")</f>
         <v>0</v>
       </c>
-      <c r="H7" s="10" t="n">
-        <f aca="false">COUNTIF(IFinancas!G2:G25,"A Fazer")+COUNTIF(IFinancas!G2:G25,"Backlog")</f>
+      <c r="H7" s="10">
+        <f>COUNTIF(IFinancas!G2:G25,"A Fazer")+COUNTIF(IFinancas!G2:G25,"Backlog")</f>
         <v>24</v>
       </c>
-      <c r="I7" s="11" t="n">
-        <f aca="false">IF(D7=0,0,E7/D7)</f>
+      <c r="I7" s="11">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J7" s="10" t="n">
-        <f aca="false">SUM(IFinancas!F2:F25)</f>
+      <c r="J7" s="10">
+        <f>SUM(IFinancas!F2:F25)</f>
         <v>25</v>
       </c>
-      <c r="K7" s="10" t="n">
-        <f aca="false">SUMIF(IFinancas!G2:G25,"Feito",IFinancas!F2:F25)</f>
+      <c r="K7" s="10">
+        <f>SUMIF(IFinancas!G2:G25,"Feito",IFinancas!F2:F25)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="2:11" ht="26.4" x14ac:dyDescent="0.3">
       <c r="B8" s="12" t="s">
         <v>16</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="6" t="n">
-        <f aca="false">COUNTA(iHelp!A2:A21)</f>
+      <c r="D8" s="6">
+        <f>COUNTA(iHelp!A2:A21)</f>
         <v>20</v>
       </c>
-      <c r="E8" s="6" t="n">
-        <f aca="false">COUNTIF(iHelp!G2:G21,"Feito")</f>
+      <c r="E8" s="6">
+        <f>COUNTIF(iHelp!G2:G21,"Feito")</f>
         <v>0</v>
       </c>
-      <c r="F8" s="6" t="n">
-        <f aca="false">COUNTIF(iHelp!G2:G21,"Fazendo")</f>
+      <c r="F8" s="6">
+        <f>COUNTIF(iHelp!G2:G21,"Fazendo")</f>
         <v>0</v>
       </c>
-      <c r="G8" s="6" t="n">
-        <f aca="false">COUNTIF(iHelp!G2:G21,"Em Review")</f>
+      <c r="G8" s="6">
+        <f>COUNTIF(iHelp!G2:G21,"Em Review")</f>
         <v>0</v>
       </c>
-      <c r="H8" s="6" t="n">
-        <f aca="false">COUNTIF(iHelp!G2:G21,"A Fazer")+COUNTIF(iHelp!G2:G21,"Backlog")</f>
+      <c r="H8" s="6">
+        <f>COUNTIF(iHelp!G2:G21,"A Fazer")+COUNTIF(iHelp!G2:G21,"Backlog")</f>
         <v>20</v>
       </c>
-      <c r="I8" s="7" t="n">
-        <f aca="false">IF(D8=0,0,E8/D8)</f>
+      <c r="I8" s="7">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J8" s="6" t="n">
-        <f aca="false">SUM(iHelp!F2:F21)</f>
+      <c r="J8" s="6">
+        <f>SUM(iHelp!F2:F21)</f>
         <v>22</v>
       </c>
-      <c r="K8" s="6" t="n">
-        <f aca="false">SUMIF(iHelp!G2:G21,"Feito",iHelp!F2:F21)</f>
+      <c r="K8" s="6">
+        <f>SUMIF(iHelp!G2:G21,"Feito",iHelp!F2:F21)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="2:11" ht="26.4" x14ac:dyDescent="0.3">
       <c r="B9" s="13" t="s">
         <v>18</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="10" t="n">
-        <f aca="false">COUNTA(IFala!A2:A24)</f>
+      <c r="D9" s="10">
+        <f>COUNTA(IFala!A2:A24)</f>
         <v>23</v>
       </c>
-      <c r="E9" s="10" t="n">
-        <f aca="false">COUNTIF(IFala!G2:G24,"Feito")</f>
+      <c r="E9" s="10">
+        <f>COUNTIF(IFala!G2:G24,"Feito")</f>
         <v>0</v>
       </c>
-      <c r="F9" s="10" t="n">
-        <f aca="false">COUNTIF(IFala!G2:G24,"Fazendo")</f>
+      <c r="F9" s="10">
+        <f>COUNTIF(IFala!G2:G24,"Fazendo")</f>
         <v>0</v>
       </c>
-      <c r="G9" s="10" t="n">
-        <f aca="false">COUNTIF(IFala!G2:G24,"Em Review")</f>
+      <c r="G9" s="10">
+        <f>COUNTIF(IFala!G2:G24,"Em Review")</f>
         <v>0</v>
       </c>
-      <c r="H9" s="10" t="n">
-        <f aca="false">COUNTIF(IFala!G2:G24,"A Fazer")+COUNTIF(IFala!G2:G24,"Backlog")</f>
+      <c r="H9" s="10">
+        <f>COUNTIF(IFala!G2:G24,"A Fazer")+COUNTIF(IFala!G2:G24,"Backlog")</f>
         <v>23</v>
       </c>
-      <c r="I9" s="11" t="n">
-        <f aca="false">IF(D9=0,0,E9/D9)</f>
+      <c r="I9" s="11">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J9" s="10" t="n">
-        <f aca="false">SUM(IFala!F2:F24)</f>
+      <c r="J9" s="10">
+        <f>SUM(IFala!F2:F24)</f>
         <v>23.5</v>
       </c>
-      <c r="K9" s="10" t="n">
-        <f aca="false">SUMIF(IFala!G2:G24,"Feito",IFala!F2:F24)</f>
+      <c r="K9" s="10">
+        <f>SUMIF(IFala!G2:G24,"Feito",IFala!F2:F24)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="2:11" ht="26.4" x14ac:dyDescent="0.3">
       <c r="B10" s="14" t="s">
         <v>20</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="6" t="n">
-        <f aca="false">COUNTA(StudyDev!A2:A24)</f>
+      <c r="D10" s="6">
+        <f>COUNTA(StudyDev!A2:A24)</f>
         <v>23</v>
       </c>
-      <c r="E10" s="6" t="n">
-        <f aca="false">COUNTIF(StudyDev!G2:G24,"Feito")</f>
+      <c r="E10" s="6">
+        <f>COUNTIF(StudyDev!G2:G24,"Feito")</f>
         <v>0</v>
       </c>
-      <c r="F10" s="6" t="n">
-        <f aca="false">COUNTIF(StudyDev!G2:G24,"Fazendo")</f>
+      <c r="F10" s="6">
+        <f>COUNTIF(StudyDev!G2:G24,"Fazendo")</f>
         <v>0</v>
       </c>
-      <c r="G10" s="6" t="n">
-        <f aca="false">COUNTIF(StudyDev!G2:G24,"Em Review")</f>
+      <c r="G10" s="6">
+        <f>COUNTIF(StudyDev!G2:G24,"Em Review")</f>
         <v>0</v>
       </c>
-      <c r="H10" s="6" t="n">
-        <f aca="false">COUNTIF(StudyDev!G2:G24,"A Fazer")+COUNTIF(StudyDev!G2:G24,"Backlog")</f>
+      <c r="H10" s="6">
+        <f>COUNTIF(StudyDev!G2:G24,"A Fazer")+COUNTIF(StudyDev!G2:G24,"Backlog")</f>
         <v>23</v>
       </c>
-      <c r="I10" s="7" t="n">
-        <f aca="false">IF(D10=0,0,E10/D10)</f>
+      <c r="I10" s="7">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J10" s="6" t="n">
-        <f aca="false">SUM(StudyDev!F2:F24)</f>
+      <c r="J10" s="6">
+        <f>SUM(StudyDev!F2:F24)</f>
         <v>26.5</v>
       </c>
-      <c r="K10" s="6" t="n">
-        <f aca="false">SUMIF(StudyDev!G2:G24,"Feito",StudyDev!F2:F24)</f>
+      <c r="K10" s="6">
+        <f>SUMIF(StudyDev!G2:G24,"Feito",StudyDev!F2:F24)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="2:11" ht="26.4" x14ac:dyDescent="0.3">
       <c r="B11" s="15" t="s">
         <v>22</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="10" t="n">
-        <f aca="false">COUNTA(MonitoraIF!A2:A20)</f>
+      <c r="D11" s="10">
+        <f>COUNTA(MonitoraIF!A2:A20)</f>
         <v>19</v>
       </c>
-      <c r="E11" s="10" t="n">
-        <f aca="false">COUNTIF(MonitoraIF!G2:G20,"Feito")</f>
+      <c r="E11" s="10">
+        <f>COUNTIF(MonitoraIF!G2:G20,"Feito")</f>
         <v>0</v>
       </c>
-      <c r="F11" s="10" t="n">
-        <f aca="false">COUNTIF(MonitoraIF!G2:G20,"Fazendo")</f>
+      <c r="F11" s="10">
+        <f>COUNTIF(MonitoraIF!G2:G20,"Fazendo")</f>
         <v>0</v>
       </c>
-      <c r="G11" s="10" t="n">
-        <f aca="false">COUNTIF(MonitoraIF!G2:G20,"Em Review")</f>
+      <c r="G11" s="10">
+        <f>COUNTIF(MonitoraIF!G2:G20,"Em Review")</f>
         <v>0</v>
       </c>
-      <c r="H11" s="10" t="n">
-        <f aca="false">COUNTIF(MonitoraIF!G2:G20,"A Fazer")+COUNTIF(MonitoraIF!G2:G20,"Backlog")</f>
+      <c r="H11" s="10">
+        <f>COUNTIF(MonitoraIF!G2:G20,"A Fazer")+COUNTIF(MonitoraIF!G2:G20,"Backlog")</f>
         <v>19</v>
       </c>
-      <c r="I11" s="11" t="n">
-        <f aca="false">IF(D11=0,0,E11/D11)</f>
+      <c r="I11" s="11">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J11" s="10" t="n">
-        <f aca="false">SUM(MonitoraIF!F2:F20)</f>
+      <c r="J11" s="10">
+        <f>SUM(MonitoraIF!F2:F20)</f>
         <v>20</v>
       </c>
-      <c r="K11" s="10" t="n">
-        <f aca="false">SUMIF(MonitoraIF!G2:G20,"Feito",MonitoraIF!F2:F20)</f>
+      <c r="K11" s="10">
+        <f>SUMIF(MonitoraIF!G2:G20,"Feito",MonitoraIF!F2:F20)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B12" s="16" t="s">
         <v>24</v>
       </c>
       <c r="C12" s="17"/>
-      <c r="D12" s="3" t="n">
-        <f aca="false">SUM(D6:D11)</f>
+      <c r="D12" s="3">
+        <f>SUM(D6:D11)</f>
         <v>135</v>
       </c>
-      <c r="E12" s="3" t="n">
-        <f aca="false">SUM(E6:E11)</f>
+      <c r="E12" s="3">
+        <f>SUM(E6:E11)</f>
         <v>0</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <f aca="false">SUM(F6:F11)</f>
+      <c r="F12" s="3">
+        <f>SUM(F6:F11)</f>
         <v>0</v>
       </c>
-      <c r="G12" s="3" t="n">
-        <f aca="false">SUM(G6:G11)</f>
+      <c r="G12" s="3">
+        <f>SUM(G6:G11)</f>
         <v>0</v>
       </c>
-      <c r="H12" s="3" t="n">
-        <f aca="false">SUM(H6:H11)</f>
+      <c r="H12" s="3">
+        <f>SUM(H6:H11)</f>
         <v>135</v>
       </c>
-      <c r="I12" s="18" t="n">
-        <f aca="false">IF(D12=0,0,E12/D12)</f>
+      <c r="I12" s="18">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J12" s="3" t="n">
-        <f aca="false">SUM(J6:J11)</f>
+      <c r="J12" s="3">
+        <f>SUM(J6:J11)</f>
         <v>142.5</v>
       </c>
-      <c r="K12" s="3" t="n">
-        <f aca="false">SUM(K6:K11)</f>
+      <c r="K12" s="3">
+        <f>SUM(K6:K11)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B14" s="19" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B15" s="20" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B16" s="20" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B17" s="20" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B18" s="20" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B19" s="20" t="s">
         <v>30</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I30"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="28"/>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="3" max="3" width="48" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="7" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>31</v>
       </c>
@@ -2327,7 +2092,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
         <v>40</v>
       </c>
@@ -2340,23 +2105,23 @@
       <c r="D2" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E2" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="6" t="n">
+      <c r="E2" s="6">
+        <v>1</v>
+      </c>
+      <c r="F2" s="6">
         <v>0.5</v>
       </c>
-      <c r="G2" s="25" t="s">
+      <c r="G2" s="6" t="s">
         <v>44</v>
       </c>
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="25" t="s">
         <v>41</v>
       </c>
       <c r="C3" s="9" t="s">
@@ -2365,19 +2130,19 @@
       <c r="D3" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E3" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="10" t="n">
+      <c r="E3" s="10">
+        <v>1</v>
+      </c>
+      <c r="F3" s="10">
         <v>1.5</v>
       </c>
-      <c r="G3" s="27" t="s">
+      <c r="G3" s="10" t="s">
         <v>44</v>
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="22" t="s">
         <v>47</v>
       </c>
@@ -2390,23 +2155,23 @@
       <c r="D4" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="25" t="s">
+      <c r="E4" s="6">
+        <v>1</v>
+      </c>
+      <c r="F4" s="6">
+        <v>1</v>
+      </c>
+      <c r="G4" s="6" t="s">
         <v>44</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="25" t="s">
         <v>41</v>
       </c>
       <c r="C5" s="9" t="s">
@@ -2415,19 +2180,19 @@
       <c r="D5" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E5" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="10" t="n">
+      <c r="E5" s="10">
+        <v>1</v>
+      </c>
+      <c r="F5" s="10">
         <v>1.5</v>
       </c>
-      <c r="G5" s="27" t="s">
+      <c r="G5" s="10" t="s">
         <v>44</v>
       </c>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="22" t="s">
         <v>51</v>
       </c>
@@ -2440,23 +2205,23 @@
       <c r="D6" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="6" t="n">
+      <c r="E6" s="6">
+        <v>1</v>
+      </c>
+      <c r="F6" s="6">
         <v>0.5</v>
       </c>
-      <c r="G6" s="25" t="s">
+      <c r="G6" s="6" t="s">
         <v>44</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="25" t="s">
         <v>52</v>
       </c>
       <c r="C7" s="9" t="s">
@@ -2465,19 +2230,19 @@
       <c r="D7" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="10" t="n">
+      <c r="E7" s="10">
+        <v>1</v>
+      </c>
+      <c r="F7" s="10">
         <v>0.5</v>
       </c>
-      <c r="G7" s="27" t="s">
+      <c r="G7" s="10" t="s">
         <v>44</v>
       </c>
       <c r="H7" s="9"/>
       <c r="I7" s="9"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="22" t="s">
         <v>56</v>
       </c>
@@ -2490,23 +2255,23 @@
       <c r="D8" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="25" t="s">
+      <c r="E8" s="6">
+        <v>1</v>
+      </c>
+      <c r="F8" s="6">
+        <v>1</v>
+      </c>
+      <c r="G8" s="6" t="s">
         <v>44</v>
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="25" t="s">
         <v>59</v>
       </c>
       <c r="C9" s="9" t="s">
@@ -2515,19 +2280,19 @@
       <c r="D9" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E9" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" s="10" t="n">
+      <c r="E9" s="10">
+        <v>2</v>
+      </c>
+      <c r="F9" s="10">
         <v>0.5</v>
       </c>
-      <c r="G9" s="27" t="s">
+      <c r="G9" s="10" t="s">
         <v>61</v>
       </c>
       <c r="H9" s="9"/>
       <c r="I9" s="9"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="22" t="s">
         <v>62</v>
       </c>
@@ -2540,23 +2305,23 @@
       <c r="D10" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" s="6" t="n">
+      <c r="E10" s="6">
+        <v>2</v>
+      </c>
+      <c r="F10" s="6">
         <v>1.5</v>
       </c>
-      <c r="G10" s="25" t="s">
+      <c r="G10" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="B11" s="26" t="s">
+      <c r="B11" s="25" t="s">
         <v>59</v>
       </c>
       <c r="C11" s="9" t="s">
@@ -2565,19 +2330,19 @@
       <c r="D11" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F11" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="27" t="s">
+      <c r="E11" s="10">
+        <v>2</v>
+      </c>
+      <c r="F11" s="10">
+        <v>1</v>
+      </c>
+      <c r="G11" s="10" t="s">
         <v>61</v>
       </c>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="22" t="s">
         <v>66</v>
       </c>
@@ -2590,23 +2355,23 @@
       <c r="D12" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="25" t="s">
+      <c r="E12" s="6">
+        <v>2</v>
+      </c>
+      <c r="F12" s="6">
+        <v>1</v>
+      </c>
+      <c r="G12" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="B13" s="26" t="s">
+      <c r="B13" s="25" t="s">
         <v>69</v>
       </c>
       <c r="C13" s="9" t="s">
@@ -2615,19 +2380,19 @@
       <c r="D13" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E13" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="27" t="s">
+      <c r="E13" s="10">
+        <v>2</v>
+      </c>
+      <c r="F13" s="10">
+        <v>1</v>
+      </c>
+      <c r="G13" s="10" t="s">
         <v>61</v>
       </c>
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="22" t="s">
         <v>71</v>
       </c>
@@ -2640,23 +2405,23 @@
       <c r="D14" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" s="6" t="n">
+      <c r="E14" s="6">
+        <v>2</v>
+      </c>
+      <c r="F14" s="6">
         <v>0.5</v>
       </c>
-      <c r="G14" s="25" t="s">
+      <c r="G14" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="B15" s="26" t="s">
+      <c r="B15" s="25" t="s">
         <v>74</v>
       </c>
       <c r="C15" s="9" t="s">
@@ -2665,19 +2430,19 @@
       <c r="D15" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F15" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="27" t="s">
+      <c r="E15" s="10">
+        <v>2</v>
+      </c>
+      <c r="F15" s="10">
+        <v>1</v>
+      </c>
+      <c r="G15" s="10" t="s">
         <v>61</v>
       </c>
       <c r="H15" s="9"/>
       <c r="I15" s="9"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="22" t="s">
         <v>76</v>
       </c>
@@ -2690,23 +2455,23 @@
       <c r="D16" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E16" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" s="25" t="s">
+      <c r="E16" s="6">
+        <v>2</v>
+      </c>
+      <c r="F16" s="6">
+        <v>1</v>
+      </c>
+      <c r="G16" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="B17" s="26" t="s">
+      <c r="B17" s="25" t="s">
         <v>79</v>
       </c>
       <c r="C17" s="9" t="s">
@@ -2715,19 +2480,19 @@
       <c r="D17" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F17" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" s="27" t="s">
+      <c r="E17" s="10">
+        <v>2</v>
+      </c>
+      <c r="F17" s="10">
+        <v>1</v>
+      </c>
+      <c r="G17" s="10" t="s">
         <v>61</v>
       </c>
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="22" t="s">
         <v>81</v>
       </c>
@@ -2740,23 +2505,23 @@
       <c r="D18" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F18" s="6" t="n">
+      <c r="E18" s="6">
+        <v>2</v>
+      </c>
+      <c r="F18" s="6">
         <v>1.5</v>
       </c>
-      <c r="G18" s="25" t="s">
+      <c r="G18" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="B19" s="26" t="s">
+      <c r="B19" s="25" t="s">
         <v>79</v>
       </c>
       <c r="C19" s="9" t="s">
@@ -2765,19 +2530,19 @@
       <c r="D19" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F19" s="10" t="n">
+      <c r="E19" s="10">
+        <v>2</v>
+      </c>
+      <c r="F19" s="10">
         <v>0.5</v>
       </c>
-      <c r="G19" s="27" t="s">
+      <c r="G19" s="10" t="s">
         <v>61</v>
       </c>
       <c r="H19" s="9"/>
       <c r="I19" s="9"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="22" t="s">
         <v>85</v>
       </c>
@@ -2790,23 +2555,23 @@
       <c r="D20" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E20" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F20" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" s="25" t="s">
+      <c r="E20" s="6">
+        <v>2</v>
+      </c>
+      <c r="F20" s="6">
+        <v>1</v>
+      </c>
+      <c r="G20" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="B21" s="26" t="s">
+      <c r="B21" s="25" t="s">
         <v>86</v>
       </c>
       <c r="C21" s="9" t="s">
@@ -2815,19 +2580,19 @@
       <c r="D21" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F21" s="10" t="n">
+      <c r="E21" s="10">
+        <v>2</v>
+      </c>
+      <c r="F21" s="10">
         <v>0.5</v>
       </c>
-      <c r="G21" s="27" t="s">
+      <c r="G21" s="10" t="s">
         <v>61</v>
       </c>
       <c r="H21" s="9"/>
       <c r="I21" s="9"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="22" t="s">
         <v>90</v>
       </c>
@@ -2837,47 +2602,47 @@
       <c r="C22" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="D22" s="28" t="s">
+      <c r="D22" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="E22" s="6">
         <v>3</v>
       </c>
-      <c r="F22" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" s="25" t="s">
+      <c r="F22" s="6">
+        <v>1</v>
+      </c>
+      <c r="G22" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="B23" s="26" t="s">
+      <c r="B23" s="25" t="s">
         <v>95</v>
       </c>
       <c r="C23" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="D23" s="28" t="s">
+      <c r="D23" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="E23" s="10" t="n">
+      <c r="E23" s="10">
         <v>3</v>
       </c>
-      <c r="F23" s="10" t="n">
+      <c r="F23" s="10">
         <v>0.5</v>
       </c>
-      <c r="G23" s="27" t="s">
+      <c r="G23" s="10" t="s">
         <v>61</v>
       </c>
       <c r="H23" s="9"/>
       <c r="I23" s="9"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="22" t="s">
         <v>97</v>
       </c>
@@ -2887,47 +2652,47 @@
       <c r="C24" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="D24" s="28" t="s">
+      <c r="D24" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="E24" s="6">
         <v>3</v>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="F24" s="6">
         <v>1.5</v>
       </c>
-      <c r="G24" s="25" t="s">
+      <c r="G24" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="B25" s="26" t="s">
+      <c r="B25" s="25" t="s">
         <v>100</v>
       </c>
       <c r="C25" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="D25" s="29" t="s">
+      <c r="D25" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="E25" s="10" t="n">
+      <c r="E25" s="10">
         <v>3</v>
       </c>
-      <c r="F25" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" s="27" t="s">
+      <c r="F25" s="10">
+        <v>1</v>
+      </c>
+      <c r="G25" s="10" t="s">
         <v>61</v>
       </c>
       <c r="H25" s="9"/>
       <c r="I25" s="9"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="22" t="s">
         <v>103</v>
       </c>
@@ -2940,23 +2705,23 @@
       <c r="D26" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="E26" s="6">
         <v>3</v>
       </c>
-      <c r="F26" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" s="25" t="s">
+      <c r="F26" s="6">
+        <v>1</v>
+      </c>
+      <c r="G26" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="B27" s="26" t="s">
+      <c r="B27" s="25" t="s">
         <v>104</v>
       </c>
       <c r="C27" s="9" t="s">
@@ -2965,104 +2730,95 @@
       <c r="D27" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E27" s="10" t="n">
+      <c r="E27" s="10">
         <v>3</v>
       </c>
-      <c r="F27" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="G27" s="27" t="s">
+      <c r="F27" s="10">
+        <v>2</v>
+      </c>
+      <c r="G27" s="10" t="s">
         <v>61</v>
       </c>
       <c r="H27" s="9"/>
       <c r="I27" s="9"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C29" s="30" t="s">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C29" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="F29" s="31" t="n">
-        <f aca="false">SUM(F2:F27)</f>
+      <c r="F29" s="29">
+        <f>SUM(F2:F27)</f>
         <v>25.5</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C30" s="30" t="s">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C30" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="F30" s="31" t="n">
-        <f aca="false">SUMIF(G2:G27,"Feito",F2:F27)</f>
+      <c r="F30" s="29">
+        <f>SUMIF(G2:G27,"Feito",F2:F27)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I27"/>
+  <autoFilter ref="A1:I27" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G2:G27" type="list">
+    <dataValidation type="list" allowBlank="1" sqref="G2:G27" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Backlog,A Fazer,Fazendo,Em Review,Feito"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:I28"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="28"/>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="3" max="3" width="48" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="7" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="32" t="s">
+    <row r="1" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A1" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="32" t="s">
+      <c r="C1" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="D1" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="32" t="s">
+      <c r="E1" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="G1" s="32" t="s">
+      <c r="G1" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="H1" s="32" t="s">
+      <c r="H1" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="I1" s="32" t="s">
+      <c r="I1" s="30" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
         <v>110</v>
       </c>
@@ -3075,23 +2831,23 @@
       <c r="D2" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E2" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="6" t="n">
+      <c r="E2" s="6">
+        <v>1</v>
+      </c>
+      <c r="F2" s="6">
         <v>0.5</v>
       </c>
-      <c r="G2" s="25" t="s">
+      <c r="G2" s="6" t="s">
         <v>44</v>
       </c>
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="25" t="s">
         <v>111</v>
       </c>
       <c r="C3" s="9" t="s">
@@ -3100,19 +2856,19 @@
       <c r="D3" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E3" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="10" t="n">
+      <c r="E3" s="10">
+        <v>1</v>
+      </c>
+      <c r="F3" s="10">
         <v>1.5</v>
       </c>
-      <c r="G3" s="27" t="s">
+      <c r="G3" s="10" t="s">
         <v>44</v>
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="22" t="s">
         <v>113</v>
       </c>
@@ -3125,23 +2881,23 @@
       <c r="D4" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="25" t="s">
+      <c r="E4" s="6">
+        <v>1</v>
+      </c>
+      <c r="F4" s="6">
+        <v>1</v>
+      </c>
+      <c r="G4" s="6" t="s">
         <v>44</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="25" t="s">
         <v>111</v>
       </c>
       <c r="C5" s="9" t="s">
@@ -3150,19 +2906,19 @@
       <c r="D5" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E5" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="10" t="n">
+      <c r="E5" s="10">
+        <v>1</v>
+      </c>
+      <c r="F5" s="10">
         <v>1.5</v>
       </c>
-      <c r="G5" s="27" t="s">
+      <c r="G5" s="10" t="s">
         <v>44</v>
       </c>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="22" t="s">
         <v>116</v>
       </c>
@@ -3175,23 +2931,23 @@
       <c r="D6" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" s="6" t="n">
+      <c r="E6" s="6">
+        <v>2</v>
+      </c>
+      <c r="F6" s="6">
         <v>0.5</v>
       </c>
-      <c r="G6" s="25" t="s">
+      <c r="G6" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="25" t="s">
         <v>117</v>
       </c>
       <c r="C7" s="9" t="s">
@@ -3200,19 +2956,19 @@
       <c r="D7" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" s="10" t="n">
+      <c r="E7" s="10">
+        <v>2</v>
+      </c>
+      <c r="F7" s="10">
         <v>1.5</v>
       </c>
-      <c r="G7" s="27" t="s">
+      <c r="G7" s="10" t="s">
         <v>61</v>
       </c>
       <c r="H7" s="9"/>
       <c r="I7" s="9"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="22" t="s">
         <v>121</v>
       </c>
@@ -3225,23 +2981,23 @@
       <c r="D8" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="25" t="s">
+      <c r="E8" s="6">
+        <v>2</v>
+      </c>
+      <c r="F8" s="6">
+        <v>1</v>
+      </c>
+      <c r="G8" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="25" t="s">
         <v>124</v>
       </c>
       <c r="C9" s="9" t="s">
@@ -3250,19 +3006,19 @@
       <c r="D9" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E9" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="27" t="s">
+      <c r="E9" s="10">
+        <v>2</v>
+      </c>
+      <c r="F9" s="10">
+        <v>1</v>
+      </c>
+      <c r="G9" s="10" t="s">
         <v>61</v>
       </c>
       <c r="H9" s="9"/>
       <c r="I9" s="9"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="22" t="s">
         <v>126</v>
       </c>
@@ -3275,23 +3031,23 @@
       <c r="D10" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="25" t="s">
+      <c r="E10" s="6">
+        <v>2</v>
+      </c>
+      <c r="F10" s="6">
+        <v>1</v>
+      </c>
+      <c r="G10" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="B11" s="26" t="s">
+      <c r="B11" s="25" t="s">
         <v>129</v>
       </c>
       <c r="C11" s="9" t="s">
@@ -3300,19 +3056,19 @@
       <c r="D11" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F11" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="27" t="s">
+      <c r="E11" s="10">
+        <v>2</v>
+      </c>
+      <c r="F11" s="10">
+        <v>1</v>
+      </c>
+      <c r="G11" s="10" t="s">
         <v>61</v>
       </c>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="22" t="s">
         <v>131</v>
       </c>
@@ -3325,23 +3081,23 @@
       <c r="D12" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="25" t="s">
+      <c r="E12" s="6">
+        <v>2</v>
+      </c>
+      <c r="F12" s="6">
+        <v>1</v>
+      </c>
+      <c r="G12" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="B13" s="26" t="s">
+      <c r="B13" s="25" t="s">
         <v>134</v>
       </c>
       <c r="C13" s="9" t="s">
@@ -3350,19 +3106,19 @@
       <c r="D13" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E13" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="27" t="s">
+      <c r="E13" s="10">
+        <v>2</v>
+      </c>
+      <c r="F13" s="10">
+        <v>1</v>
+      </c>
+      <c r="G13" s="10" t="s">
         <v>61</v>
       </c>
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="22" t="s">
         <v>136</v>
       </c>
@@ -3375,23 +3131,23 @@
       <c r="D14" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="25" t="s">
+      <c r="E14" s="6">
+        <v>2</v>
+      </c>
+      <c r="F14" s="6">
+        <v>1</v>
+      </c>
+      <c r="G14" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="B15" s="26" t="s">
+      <c r="B15" s="25" t="s">
         <v>134</v>
       </c>
       <c r="C15" s="9" t="s">
@@ -3400,19 +3156,19 @@
       <c r="D15" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F15" s="10" t="n">
+      <c r="E15" s="10">
+        <v>2</v>
+      </c>
+      <c r="F15" s="10">
         <v>0.5</v>
       </c>
-      <c r="G15" s="27" t="s">
+      <c r="G15" s="10" t="s">
         <v>61</v>
       </c>
       <c r="H15" s="9"/>
       <c r="I15" s="9"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="22" t="s">
         <v>140</v>
       </c>
@@ -3425,23 +3181,23 @@
       <c r="D16" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E16" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" s="25" t="s">
+      <c r="E16" s="6">
+        <v>2</v>
+      </c>
+      <c r="F16" s="6">
+        <v>1</v>
+      </c>
+      <c r="G16" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="B17" s="26" t="s">
+      <c r="B17" s="25" t="s">
         <v>141</v>
       </c>
       <c r="C17" s="9" t="s">
@@ -3450,19 +3206,19 @@
       <c r="D17" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F17" s="10" t="n">
+      <c r="E17" s="10">
+        <v>2</v>
+      </c>
+      <c r="F17" s="10">
         <v>1.5</v>
       </c>
-      <c r="G17" s="27" t="s">
+      <c r="G17" s="10" t="s">
         <v>61</v>
       </c>
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="22" t="s">
         <v>145</v>
       </c>
@@ -3472,47 +3228,47 @@
       <c r="C18" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="D18" s="28" t="s">
+      <c r="D18" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="E18" s="6">
         <v>3</v>
       </c>
-      <c r="F18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="25" t="s">
+      <c r="F18" s="6">
+        <v>1</v>
+      </c>
+      <c r="G18" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="B19" s="26" t="s">
+      <c r="B19" s="25" t="s">
         <v>146</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="D19" s="28" t="s">
+      <c r="D19" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="E19" s="10" t="n">
+      <c r="E19" s="10">
         <v>3</v>
       </c>
-      <c r="F19" s="10" t="n">
+      <c r="F19" s="10">
         <v>0.5</v>
       </c>
-      <c r="G19" s="27" t="s">
+      <c r="G19" s="10" t="s">
         <v>61</v>
       </c>
       <c r="H19" s="9"/>
       <c r="I19" s="9"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="22" t="s">
         <v>150</v>
       </c>
@@ -3522,47 +3278,47 @@
       <c r="C20" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="D20" s="28" t="s">
+      <c r="D20" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="E20" s="6">
         <v>3</v>
       </c>
-      <c r="F20" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" s="25" t="s">
+      <c r="F20" s="6">
+        <v>1</v>
+      </c>
+      <c r="G20" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="B21" s="26" t="s">
+      <c r="B21" s="25" t="s">
         <v>151</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="D21" s="28" t="s">
+      <c r="D21" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="E21" s="10" t="n">
+      <c r="E21" s="10">
         <v>3</v>
       </c>
-      <c r="F21" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" s="27" t="s">
+      <c r="F21" s="10">
+        <v>1</v>
+      </c>
+      <c r="G21" s="10" t="s">
         <v>61</v>
       </c>
       <c r="H21" s="9"/>
       <c r="I21" s="9"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="22" t="s">
         <v>155</v>
       </c>
@@ -3572,47 +3328,47 @@
       <c r="C22" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="D22" s="28" t="s">
+      <c r="D22" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="E22" s="6">
         <v>3</v>
       </c>
-      <c r="F22" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" s="25" t="s">
+      <c r="F22" s="6">
+        <v>1</v>
+      </c>
+      <c r="G22" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="B23" s="26" t="s">
+      <c r="B23" s="25" t="s">
         <v>156</v>
       </c>
       <c r="C23" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="D23" s="28" t="s">
+      <c r="D23" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="E23" s="10" t="n">
+      <c r="E23" s="10">
         <v>3</v>
       </c>
-      <c r="F23" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="27" t="s">
+      <c r="F23" s="10">
+        <v>1</v>
+      </c>
+      <c r="G23" s="10" t="s">
         <v>61</v>
       </c>
       <c r="H23" s="9"/>
       <c r="I23" s="9"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="22" t="s">
         <v>160</v>
       </c>
@@ -3625,23 +3381,23 @@
       <c r="D24" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="E24" s="6">
         <v>3</v>
       </c>
-      <c r="F24" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="25" t="s">
+      <c r="F24" s="6">
+        <v>1</v>
+      </c>
+      <c r="G24" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="B25" s="26" t="s">
+      <c r="B25" s="25" t="s">
         <v>104</v>
       </c>
       <c r="C25" s="9" t="s">
@@ -3650,104 +3406,95 @@
       <c r="D25" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E25" s="10" t="n">
+      <c r="E25" s="10">
         <v>3</v>
       </c>
-      <c r="F25" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="G25" s="27" t="s">
+      <c r="F25" s="10">
+        <v>2</v>
+      </c>
+      <c r="G25" s="10" t="s">
         <v>61</v>
       </c>
       <c r="H25" s="9"/>
       <c r="I25" s="9"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C27" s="30" t="s">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C27" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="F27" s="31" t="n">
-        <f aca="false">SUM(F2:F25)</f>
+      <c r="F27" s="29">
+        <f>SUM(F2:F25)</f>
         <v>25</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C28" s="30" t="s">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C28" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="F28" s="31" t="n">
-        <f aca="false">SUMIF(G2:G25,"Feito",F2:F25)</f>
+      <c r="F28" s="29">
+        <f>SUMIF(G2:G25,"Feito",F2:F25)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I25"/>
+  <autoFilter ref="A1:I25" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G2:G25" type="list">
+    <dataValidation type="list" allowBlank="1" sqref="G2:G25" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Backlog,A Fazer,Fazendo,Em Review,Feito"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:I24"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="28"/>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="3" max="3" width="48" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="7" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="33" t="s">
+    <row r="1" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A1" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="C1" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="E1" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="G1" s="33" t="s">
+      <c r="G1" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="H1" s="33" t="s">
+      <c r="H1" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="I1" s="33" t="s">
+      <c r="I1" s="31" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
         <v>162</v>
       </c>
@@ -3760,23 +3507,23 @@
       <c r="D2" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E2" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="6" t="n">
+      <c r="E2" s="6">
+        <v>1</v>
+      </c>
+      <c r="F2" s="6">
         <v>0.5</v>
       </c>
-      <c r="G2" s="25" t="s">
+      <c r="G2" s="6" t="s">
         <v>44</v>
       </c>
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="25" t="s">
         <v>163</v>
       </c>
       <c r="C3" s="9" t="s">
@@ -3785,19 +3532,19 @@
       <c r="D3" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E3" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="10" t="n">
+      <c r="E3" s="10">
+        <v>1</v>
+      </c>
+      <c r="F3" s="10">
         <v>1.5</v>
       </c>
-      <c r="G3" s="27" t="s">
+      <c r="G3" s="10" t="s">
         <v>44</v>
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="22" t="s">
         <v>166</v>
       </c>
@@ -3810,23 +3557,23 @@
       <c r="D4" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="25" t="s">
+      <c r="E4" s="6">
+        <v>1</v>
+      </c>
+      <c r="F4" s="6">
+        <v>1</v>
+      </c>
+      <c r="G4" s="6" t="s">
         <v>44</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="25" t="s">
         <v>163</v>
       </c>
       <c r="C5" s="9" t="s">
@@ -3835,19 +3582,19 @@
       <c r="D5" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E5" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="10" t="n">
+      <c r="E5" s="10">
+        <v>1</v>
+      </c>
+      <c r="F5" s="10">
         <v>1.5</v>
       </c>
-      <c r="G5" s="27" t="s">
+      <c r="G5" s="10" t="s">
         <v>44</v>
       </c>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="22" t="s">
         <v>169</v>
       </c>
@@ -3860,23 +3607,23 @@
       <c r="D6" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="6" t="n">
+      <c r="E6" s="6">
+        <v>1</v>
+      </c>
+      <c r="F6" s="6">
         <v>0.5</v>
       </c>
-      <c r="G6" s="25" t="s">
+      <c r="G6" s="6" t="s">
         <v>44</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="25" t="s">
         <v>170</v>
       </c>
       <c r="C7" s="9" t="s">
@@ -3885,19 +3632,19 @@
       <c r="D7" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="10" t="n">
+      <c r="E7" s="10">
+        <v>1</v>
+      </c>
+      <c r="F7" s="10">
         <v>1.5</v>
       </c>
-      <c r="G7" s="27" t="s">
+      <c r="G7" s="10" t="s">
         <v>44</v>
       </c>
       <c r="H7" s="9"/>
       <c r="I7" s="9"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="22" t="s">
         <v>174</v>
       </c>
@@ -3910,23 +3657,23 @@
       <c r="D8" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="25" t="s">
+      <c r="E8" s="6">
+        <v>1</v>
+      </c>
+      <c r="F8" s="6">
+        <v>1</v>
+      </c>
+      <c r="G8" s="6" t="s">
         <v>44</v>
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="25" t="s">
         <v>177</v>
       </c>
       <c r="C9" s="9" t="s">
@@ -3935,19 +3682,19 @@
       <c r="D9" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E9" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="27" t="s">
+      <c r="E9" s="10">
+        <v>2</v>
+      </c>
+      <c r="F9" s="10">
+        <v>1</v>
+      </c>
+      <c r="G9" s="10" t="s">
         <v>61</v>
       </c>
       <c r="H9" s="9"/>
       <c r="I9" s="9"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="22" t="s">
         <v>179</v>
       </c>
@@ -3960,23 +3707,23 @@
       <c r="D10" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="25" t="s">
+      <c r="E10" s="6">
+        <v>2</v>
+      </c>
+      <c r="F10" s="6">
+        <v>1</v>
+      </c>
+      <c r="G10" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="B11" s="26" t="s">
+      <c r="B11" s="25" t="s">
         <v>182</v>
       </c>
       <c r="C11" s="9" t="s">
@@ -3985,19 +3732,19 @@
       <c r="D11" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F11" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="27" t="s">
+      <c r="E11" s="10">
+        <v>2</v>
+      </c>
+      <c r="F11" s="10">
+        <v>1</v>
+      </c>
+      <c r="G11" s="10" t="s">
         <v>61</v>
       </c>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="22" t="s">
         <v>184</v>
       </c>
@@ -4010,23 +3757,23 @@
       <c r="D12" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="25" t="s">
+      <c r="E12" s="6">
+        <v>2</v>
+      </c>
+      <c r="F12" s="6">
+        <v>1</v>
+      </c>
+      <c r="G12" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="B13" s="26" t="s">
+      <c r="B13" s="25" t="s">
         <v>187</v>
       </c>
       <c r="C13" s="9" t="s">
@@ -4035,19 +3782,19 @@
       <c r="D13" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E13" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" s="10" t="n">
+      <c r="E13" s="10">
+        <v>2</v>
+      </c>
+      <c r="F13" s="10">
         <v>0.5</v>
       </c>
-      <c r="G13" s="27" t="s">
+      <c r="G13" s="10" t="s">
         <v>61</v>
       </c>
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="22" t="s">
         <v>189</v>
       </c>
@@ -4060,23 +3807,23 @@
       <c r="D14" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" s="6" t="n">
+      <c r="E14" s="6">
+        <v>2</v>
+      </c>
+      <c r="F14" s="6">
         <v>1.5</v>
       </c>
-      <c r="G14" s="25" t="s">
+      <c r="G14" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
         <v>191</v>
       </c>
-      <c r="B15" s="26" t="s">
+      <c r="B15" s="25" t="s">
         <v>192</v>
       </c>
       <c r="C15" s="9" t="s">
@@ -4085,19 +3832,19 @@
       <c r="D15" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F15" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="27" t="s">
+      <c r="E15" s="10">
+        <v>2</v>
+      </c>
+      <c r="F15" s="10">
+        <v>1</v>
+      </c>
+      <c r="G15" s="10" t="s">
         <v>61</v>
       </c>
       <c r="H15" s="9"/>
       <c r="I15" s="9"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="22" t="s">
         <v>194</v>
       </c>
@@ -4107,47 +3854,47 @@
       <c r="C16" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="D16" s="28" t="s">
+      <c r="D16" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="E16" s="6">
         <v>3</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="F16" s="6">
         <v>1.5</v>
       </c>
-      <c r="G16" s="25" t="s">
+      <c r="G16" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="B17" s="26" t="s">
+      <c r="B17" s="25" t="s">
         <v>195</v>
       </c>
       <c r="C17" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="D17" s="28" t="s">
+      <c r="D17" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="E17" s="10" t="n">
+      <c r="E17" s="10">
         <v>3</v>
       </c>
-      <c r="F17" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" s="27" t="s">
+      <c r="F17" s="10">
+        <v>1</v>
+      </c>
+      <c r="G17" s="10" t="s">
         <v>61</v>
       </c>
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="22" t="s">
         <v>199</v>
       </c>
@@ -4157,47 +3904,47 @@
       <c r="C18" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="D18" s="28" t="s">
+      <c r="D18" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="E18" s="6">
         <v>3</v>
       </c>
-      <c r="F18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="25" t="s">
+      <c r="F18" s="6">
+        <v>1</v>
+      </c>
+      <c r="G18" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="15" t="s">
         <v>202</v>
       </c>
-      <c r="B19" s="26" t="s">
+      <c r="B19" s="25" t="s">
         <v>203</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="D19" s="28" t="s">
+      <c r="D19" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="E19" s="10" t="n">
+      <c r="E19" s="10">
         <v>3</v>
       </c>
-      <c r="F19" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" s="27" t="s">
+      <c r="F19" s="10">
+        <v>1</v>
+      </c>
+      <c r="G19" s="10" t="s">
         <v>61</v>
       </c>
       <c r="H19" s="9"/>
       <c r="I19" s="9"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="22" t="s">
         <v>205</v>
       </c>
@@ -4210,23 +3957,23 @@
       <c r="D20" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="E20" s="6">
         <v>3</v>
       </c>
-      <c r="F20" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" s="25" t="s">
+      <c r="F20" s="6">
+        <v>1</v>
+      </c>
+      <c r="G20" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="15" t="s">
         <v>206</v>
       </c>
-      <c r="B21" s="26" t="s">
+      <c r="B21" s="25" t="s">
         <v>104</v>
       </c>
       <c r="C21" s="9" t="s">
@@ -4235,104 +3982,95 @@
       <c r="D21" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="10" t="n">
+      <c r="E21" s="10">
         <v>3</v>
       </c>
-      <c r="F21" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="G21" s="27" t="s">
+      <c r="F21" s="10">
+        <v>2</v>
+      </c>
+      <c r="G21" s="10" t="s">
         <v>61</v>
       </c>
       <c r="H21" s="9"/>
       <c r="I21" s="9"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C23" s="30" t="s">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C23" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="F23" s="31" t="n">
-        <f aca="false">SUM(F2:F21)</f>
+      <c r="F23" s="29">
+        <f>SUM(F2:F21)</f>
         <v>22</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C24" s="30" t="s">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C24" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="F24" s="31" t="n">
-        <f aca="false">SUMIF(G2:G21,"Feito",F2:F21)</f>
+      <c r="F24" s="29">
+        <f>SUMIF(G2:G21,"Feito",F2:F21)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I21"/>
+  <autoFilter ref="A1:I21" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G2:G21" type="list">
+    <dataValidation type="list" allowBlank="1" sqref="G2:G21" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"Backlog,A Fazer,Fazendo,Em Review,Feito"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:I27"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="28"/>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="3" max="3" width="48" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="7" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="34" t="s">
+    <row r="1" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A1" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="34" t="s">
+      <c r="B1" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="34" t="s">
+      <c r="C1" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="D1" s="34" t="s">
+      <c r="D1" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="34" t="s">
+      <c r="E1" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="34" t="s">
+      <c r="F1" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="G1" s="34" t="s">
+      <c r="G1" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="H1" s="34" t="s">
+      <c r="H1" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="I1" s="34" t="s">
+      <c r="I1" s="32" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
         <v>207</v>
       </c>
@@ -4345,23 +4083,23 @@
       <c r="D2" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E2" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="6" t="n">
+      <c r="E2" s="6">
+        <v>1</v>
+      </c>
+      <c r="F2" s="6">
         <v>0.5</v>
       </c>
-      <c r="G2" s="25" t="s">
+      <c r="G2" s="6" t="s">
         <v>44</v>
       </c>
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
         <v>209</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="25" t="s">
         <v>208</v>
       </c>
       <c r="C3" s="9" t="s">
@@ -4370,19 +4108,19 @@
       <c r="D3" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E3" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="10" t="n">
+      <c r="E3" s="10">
+        <v>1</v>
+      </c>
+      <c r="F3" s="10">
         <v>1.5</v>
       </c>
-      <c r="G3" s="27" t="s">
+      <c r="G3" s="10" t="s">
         <v>44</v>
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="22" t="s">
         <v>210</v>
       </c>
@@ -4395,23 +4133,23 @@
       <c r="D4" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="25" t="s">
+      <c r="E4" s="6">
+        <v>1</v>
+      </c>
+      <c r="F4" s="6">
+        <v>1</v>
+      </c>
+      <c r="G4" s="6" t="s">
         <v>44</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
         <v>212</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="25" t="s">
         <v>208</v>
       </c>
       <c r="C5" s="9" t="s">
@@ -4420,19 +4158,19 @@
       <c r="D5" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E5" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="27" t="s">
+      <c r="E5" s="10">
+        <v>1</v>
+      </c>
+      <c r="F5" s="10">
+        <v>1</v>
+      </c>
+      <c r="G5" s="10" t="s">
         <v>44</v>
       </c>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="22" t="s">
         <v>214</v>
       </c>
@@ -4445,23 +4183,23 @@
       <c r="D6" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="6" t="n">
+      <c r="E6" s="6">
+        <v>1</v>
+      </c>
+      <c r="F6" s="6">
         <v>0.5</v>
       </c>
-      <c r="G6" s="25" t="s">
+      <c r="G6" s="6" t="s">
         <v>44</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
         <v>217</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="25" t="s">
         <v>215</v>
       </c>
       <c r="C7" s="9" t="s">
@@ -4470,19 +4208,19 @@
       <c r="D7" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="27" t="s">
+      <c r="E7" s="10">
+        <v>1</v>
+      </c>
+      <c r="F7" s="10">
+        <v>1</v>
+      </c>
+      <c r="G7" s="10" t="s">
         <v>44</v>
       </c>
       <c r="H7" s="9"/>
       <c r="I7" s="9"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="22" t="s">
         <v>219</v>
       </c>
@@ -4495,23 +4233,23 @@
       <c r="D8" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" s="6" t="n">
+      <c r="E8" s="6">
+        <v>2</v>
+      </c>
+      <c r="F8" s="6">
         <v>0.5</v>
       </c>
-      <c r="G8" s="25" t="s">
+      <c r="G8" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
         <v>222</v>
       </c>
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="25" t="s">
         <v>220</v>
       </c>
       <c r="C9" s="9" t="s">
@@ -4520,19 +4258,19 @@
       <c r="D9" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E9" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="27" t="s">
+      <c r="E9" s="10">
+        <v>2</v>
+      </c>
+      <c r="F9" s="10">
+        <v>1</v>
+      </c>
+      <c r="G9" s="10" t="s">
         <v>61</v>
       </c>
       <c r="H9" s="9"/>
       <c r="I9" s="9"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="22" t="s">
         <v>224</v>
       </c>
@@ -4545,23 +4283,23 @@
       <c r="D10" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="25" t="s">
+      <c r="E10" s="6">
+        <v>2</v>
+      </c>
+      <c r="F10" s="6">
+        <v>1</v>
+      </c>
+      <c r="G10" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
         <v>226</v>
       </c>
-      <c r="B11" s="26" t="s">
+      <c r="B11" s="25" t="s">
         <v>227</v>
       </c>
       <c r="C11" s="9" t="s">
@@ -4570,19 +4308,19 @@
       <c r="D11" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F11" s="10" t="n">
+      <c r="E11" s="10">
+        <v>2</v>
+      </c>
+      <c r="F11" s="10">
         <v>1.5</v>
       </c>
-      <c r="G11" s="27" t="s">
+      <c r="G11" s="10" t="s">
         <v>61</v>
       </c>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="22" t="s">
         <v>229</v>
       </c>
@@ -4595,23 +4333,23 @@
       <c r="D12" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" s="6" t="n">
+      <c r="E12" s="6">
+        <v>2</v>
+      </c>
+      <c r="F12" s="6">
         <v>0.5</v>
       </c>
-      <c r="G12" s="25" t="s">
+      <c r="G12" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
         <v>231</v>
       </c>
-      <c r="B13" s="26" t="s">
+      <c r="B13" s="25" t="s">
         <v>232</v>
       </c>
       <c r="C13" s="9" t="s">
@@ -4620,19 +4358,19 @@
       <c r="D13" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E13" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="27" t="s">
+      <c r="E13" s="10">
+        <v>2</v>
+      </c>
+      <c r="F13" s="10">
+        <v>1</v>
+      </c>
+      <c r="G13" s="10" t="s">
         <v>61</v>
       </c>
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="22" t="s">
         <v>234</v>
       </c>
@@ -4645,23 +4383,23 @@
       <c r="D14" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="25" t="s">
+      <c r="E14" s="6">
+        <v>2</v>
+      </c>
+      <c r="F14" s="6">
+        <v>1</v>
+      </c>
+      <c r="G14" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
         <v>236</v>
       </c>
-      <c r="B15" s="26" t="s">
+      <c r="B15" s="25" t="s">
         <v>237</v>
       </c>
       <c r="C15" s="9" t="s">
@@ -4670,19 +4408,19 @@
       <c r="D15" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F15" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="27" t="s">
+      <c r="E15" s="10">
+        <v>2</v>
+      </c>
+      <c r="F15" s="10">
+        <v>1</v>
+      </c>
+      <c r="G15" s="10" t="s">
         <v>61</v>
       </c>
       <c r="H15" s="9"/>
       <c r="I15" s="9"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="22" t="s">
         <v>239</v>
       </c>
@@ -4695,23 +4433,23 @@
       <c r="D16" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E16" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" s="25" t="s">
+      <c r="E16" s="6">
+        <v>2</v>
+      </c>
+      <c r="F16" s="6">
+        <v>1</v>
+      </c>
+      <c r="G16" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
         <v>241</v>
       </c>
-      <c r="B17" s="26" t="s">
+      <c r="B17" s="25" t="s">
         <v>242</v>
       </c>
       <c r="C17" s="9" t="s">
@@ -4720,19 +4458,19 @@
       <c r="D17" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F17" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" s="27" t="s">
+      <c r="E17" s="10">
+        <v>2</v>
+      </c>
+      <c r="F17" s="10">
+        <v>1</v>
+      </c>
+      <c r="G17" s="10" t="s">
         <v>61</v>
       </c>
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="22" t="s">
         <v>244</v>
       </c>
@@ -4745,44 +4483,44 @@
       <c r="D18" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="25" t="s">
+      <c r="E18" s="6">
+        <v>2</v>
+      </c>
+      <c r="F18" s="6">
+        <v>1</v>
+      </c>
+      <c r="G18" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="15" t="s">
         <v>246</v>
       </c>
-      <c r="B19" s="26" t="s">
+      <c r="B19" s="25" t="s">
         <v>247</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="D19" s="28" t="s">
+      <c r="D19" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="E19" s="10" t="n">
+      <c r="E19" s="10">
         <v>3</v>
       </c>
-      <c r="F19" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" s="27" t="s">
+      <c r="F19" s="10">
+        <v>1</v>
+      </c>
+      <c r="G19" s="10" t="s">
         <v>61</v>
       </c>
       <c r="H19" s="9"/>
       <c r="I19" s="9"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="22" t="s">
         <v>249</v>
       </c>
@@ -4792,47 +4530,47 @@
       <c r="C20" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="D20" s="28" t="s">
+      <c r="D20" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="E20" s="6">
         <v>3</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="F20" s="6">
         <v>1.5</v>
       </c>
-      <c r="G20" s="25" t="s">
+      <c r="G20" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="15" t="s">
         <v>252</v>
       </c>
-      <c r="B21" s="26" t="s">
+      <c r="B21" s="25" t="s">
         <v>250</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="D21" s="28" t="s">
+      <c r="D21" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="E21" s="10" t="n">
+      <c r="E21" s="10">
         <v>3</v>
       </c>
-      <c r="F21" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" s="27" t="s">
+      <c r="F21" s="10">
+        <v>1</v>
+      </c>
+      <c r="G21" s="10" t="s">
         <v>61</v>
       </c>
       <c r="H21" s="9"/>
       <c r="I21" s="9"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="22" t="s">
         <v>254</v>
       </c>
@@ -4845,23 +4583,23 @@
       <c r="D22" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="E22" s="6">
         <v>3</v>
       </c>
-      <c r="F22" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" s="25" t="s">
+      <c r="F22" s="6">
+        <v>1</v>
+      </c>
+      <c r="G22" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="15" t="s">
         <v>255</v>
       </c>
-      <c r="B23" s="26" t="s">
+      <c r="B23" s="25" t="s">
         <v>104</v>
       </c>
       <c r="C23" s="9" t="s">
@@ -4870,19 +4608,19 @@
       <c r="D23" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E23" s="10" t="n">
+      <c r="E23" s="10">
         <v>3</v>
       </c>
-      <c r="F23" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="G23" s="27" t="s">
+      <c r="F23" s="10">
+        <v>2</v>
+      </c>
+      <c r="G23" s="10" t="s">
         <v>61</v>
       </c>
       <c r="H23" s="9"/>
       <c r="I23" s="9"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="22" t="s">
         <v>256</v>
       </c>
@@ -4895,104 +4633,95 @@
       <c r="D24" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="E24" s="6">
         <v>3</v>
       </c>
-      <c r="F24" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="25" t="s">
+      <c r="F24" s="6">
+        <v>1</v>
+      </c>
+      <c r="G24" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C26" s="30" t="s">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C26" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="F26" s="31" t="n">
-        <f aca="false">SUM(F2:F24)</f>
+      <c r="F26" s="29">
+        <f>SUM(F2:F24)</f>
         <v>23.5</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C27" s="30" t="s">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C27" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="F27" s="31" t="n">
-        <f aca="false">SUMIF(G2:G24,"Feito",F2:F24)</f>
+      <c r="F27" s="29">
+        <f>SUMIF(G2:G24,"Feito",F2:F24)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I24"/>
+  <autoFilter ref="A1:I24" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G2:G24" type="list">
+    <dataValidation type="list" allowBlank="1" sqref="G2:G24" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"Backlog,A Fazer,Fazendo,Em Review,Feito"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:I27"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="28"/>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="3" max="3" width="48" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="7" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="35" t="s">
+    <row r="1" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A1" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="35" t="s">
+      <c r="B1" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="35" t="s">
+      <c r="C1" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="D1" s="35" t="s">
+      <c r="D1" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="35" t="s">
+      <c r="E1" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="F1" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="G1" s="35" t="s">
+      <c r="G1" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="H1" s="35" t="s">
+      <c r="H1" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="I1" s="35" t="s">
+      <c r="I1" s="33" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
         <v>258</v>
       </c>
@@ -5005,23 +4734,23 @@
       <c r="D2" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E2" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="6" t="n">
+      <c r="E2" s="6">
+        <v>1</v>
+      </c>
+      <c r="F2" s="6">
         <v>0.5</v>
       </c>
-      <c r="G2" s="25" t="s">
+      <c r="G2" s="6" t="s">
         <v>44</v>
       </c>
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
         <v>260</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="25" t="s">
         <v>259</v>
       </c>
       <c r="C3" s="9" t="s">
@@ -5030,19 +4759,19 @@
       <c r="D3" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E3" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="10" t="n">
+      <c r="E3" s="10">
+        <v>1</v>
+      </c>
+      <c r="F3" s="10">
         <v>1.5</v>
       </c>
-      <c r="G3" s="27" t="s">
+      <c r="G3" s="10" t="s">
         <v>44</v>
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="22" t="s">
         <v>261</v>
       </c>
@@ -5055,23 +4784,23 @@
       <c r="D4" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="6" t="n">
+      <c r="E4" s="6">
+        <v>1</v>
+      </c>
+      <c r="F4" s="6">
         <v>1.5</v>
       </c>
-      <c r="G4" s="25" t="s">
+      <c r="G4" s="6" t="s">
         <v>44</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
         <v>263</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="25" t="s">
         <v>264</v>
       </c>
       <c r="C5" s="9" t="s">
@@ -5080,19 +4809,19 @@
       <c r="D5" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E5" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="10" t="n">
+      <c r="E5" s="10">
+        <v>1</v>
+      </c>
+      <c r="F5" s="10">
         <v>0.5</v>
       </c>
-      <c r="G5" s="27" t="s">
+      <c r="G5" s="10" t="s">
         <v>44</v>
       </c>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="22" t="s">
         <v>266</v>
       </c>
@@ -5105,23 +4834,23 @@
       <c r="D6" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="6" t="n">
+      <c r="E6" s="6">
+        <v>1</v>
+      </c>
+      <c r="F6" s="6">
         <v>1.5</v>
       </c>
-      <c r="G6" s="25" t="s">
+      <c r="G6" s="6" t="s">
         <v>44</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
         <v>268</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="25" t="s">
         <v>269</v>
       </c>
       <c r="C7" s="9" t="s">
@@ -5130,19 +4859,19 @@
       <c r="D7" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="27" t="s">
+      <c r="E7" s="10">
+        <v>1</v>
+      </c>
+      <c r="F7" s="10">
+        <v>1</v>
+      </c>
+      <c r="G7" s="10" t="s">
         <v>44</v>
       </c>
       <c r="H7" s="9"/>
       <c r="I7" s="9"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="22" t="s">
         <v>271</v>
       </c>
@@ -5155,23 +4884,23 @@
       <c r="D8" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" s="25" t="s">
+      <c r="E8" s="6">
+        <v>1</v>
+      </c>
+      <c r="F8" s="6">
+        <v>2</v>
+      </c>
+      <c r="G8" s="6" t="s">
         <v>44</v>
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="25" t="s">
         <v>269</v>
       </c>
       <c r="C9" s="9" t="s">
@@ -5180,19 +4909,19 @@
       <c r="D9" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E9" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" s="27" t="s">
+      <c r="E9" s="10">
+        <v>1</v>
+      </c>
+      <c r="F9" s="10">
+        <v>2</v>
+      </c>
+      <c r="G9" s="10" t="s">
         <v>44</v>
       </c>
       <c r="H9" s="9"/>
       <c r="I9" s="9"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="22" t="s">
         <v>275</v>
       </c>
@@ -5205,23 +4934,23 @@
       <c r="D10" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="25" t="s">
+      <c r="E10" s="6">
+        <v>2</v>
+      </c>
+      <c r="F10" s="6">
+        <v>1</v>
+      </c>
+      <c r="G10" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
         <v>277</v>
       </c>
-      <c r="B11" s="26" t="s">
+      <c r="B11" s="25" t="s">
         <v>278</v>
       </c>
       <c r="C11" s="9" t="s">
@@ -5230,19 +4959,19 @@
       <c r="D11" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F11" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="27" t="s">
+      <c r="E11" s="10">
+        <v>2</v>
+      </c>
+      <c r="F11" s="10">
+        <v>1</v>
+      </c>
+      <c r="G11" s="10" t="s">
         <v>61</v>
       </c>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="22" t="s">
         <v>280</v>
       </c>
@@ -5255,23 +4984,23 @@
       <c r="D12" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="25" t="s">
+      <c r="E12" s="6">
+        <v>2</v>
+      </c>
+      <c r="F12" s="6">
+        <v>1</v>
+      </c>
+      <c r="G12" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
         <v>282</v>
       </c>
-      <c r="B13" s="26" t="s">
+      <c r="B13" s="25" t="s">
         <v>283</v>
       </c>
       <c r="C13" s="9" t="s">
@@ -5280,19 +5009,19 @@
       <c r="D13" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E13" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" s="10" t="n">
+      <c r="E13" s="10">
+        <v>2</v>
+      </c>
+      <c r="F13" s="10">
         <v>1.5</v>
       </c>
-      <c r="G13" s="27" t="s">
+      <c r="G13" s="10" t="s">
         <v>61</v>
       </c>
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="22" t="s">
         <v>285</v>
       </c>
@@ -5305,23 +5034,23 @@
       <c r="D14" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" s="6" t="n">
+      <c r="E14" s="6">
+        <v>2</v>
+      </c>
+      <c r="F14" s="6">
         <v>0.5</v>
       </c>
-      <c r="G14" s="25" t="s">
+      <c r="G14" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="B15" s="26" t="s">
+      <c r="B15" s="25" t="s">
         <v>288</v>
       </c>
       <c r="C15" s="9" t="s">
@@ -5330,19 +5059,19 @@
       <c r="D15" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F15" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="27" t="s">
+      <c r="E15" s="10">
+        <v>2</v>
+      </c>
+      <c r="F15" s="10">
+        <v>1</v>
+      </c>
+      <c r="G15" s="10" t="s">
         <v>61</v>
       </c>
       <c r="H15" s="9"/>
       <c r="I15" s="9"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="22" t="s">
         <v>290</v>
       </c>
@@ -5355,44 +5084,44 @@
       <c r="D16" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E16" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" s="25" t="s">
+      <c r="E16" s="6">
+        <v>2</v>
+      </c>
+      <c r="F16" s="6">
+        <v>1</v>
+      </c>
+      <c r="G16" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
         <v>292</v>
       </c>
-      <c r="B17" s="26" t="s">
+      <c r="B17" s="25" t="s">
         <v>293</v>
       </c>
       <c r="C17" s="9" t="s">
         <v>294</v>
       </c>
-      <c r="D17" s="28" t="s">
+      <c r="D17" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="E17" s="10" t="n">
+      <c r="E17" s="10">
         <v>3</v>
       </c>
-      <c r="F17" s="10" t="n">
+      <c r="F17" s="10">
         <v>1.5</v>
       </c>
-      <c r="G17" s="27" t="s">
+      <c r="G17" s="10" t="s">
         <v>61</v>
       </c>
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="22" t="s">
         <v>295</v>
       </c>
@@ -5402,47 +5131,47 @@
       <c r="C18" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="D18" s="28" t="s">
+      <c r="D18" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="E18" s="6">
         <v>3</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="F18" s="6">
         <v>0.5</v>
       </c>
-      <c r="G18" s="25" t="s">
+      <c r="G18" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="15" t="s">
         <v>297</v>
       </c>
-      <c r="B19" s="26" t="s">
+      <c r="B19" s="25" t="s">
         <v>298</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="D19" s="28" t="s">
+      <c r="D19" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="E19" s="10" t="n">
+      <c r="E19" s="10">
         <v>3</v>
       </c>
-      <c r="F19" s="10" t="n">
+      <c r="F19" s="10">
         <v>0.5</v>
       </c>
-      <c r="G19" s="27" t="s">
+      <c r="G19" s="10" t="s">
         <v>61</v>
       </c>
       <c r="H19" s="9"/>
       <c r="I19" s="9"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="22" t="s">
         <v>299</v>
       </c>
@@ -5452,47 +5181,47 @@
       <c r="C20" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="D20" s="28" t="s">
+      <c r="D20" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="E20" s="6">
         <v>3</v>
       </c>
-      <c r="F20" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" s="25" t="s">
+      <c r="F20" s="6">
+        <v>1</v>
+      </c>
+      <c r="G20" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="15" t="s">
         <v>301</v>
       </c>
-      <c r="B21" s="26" t="s">
+      <c r="B21" s="25" t="s">
         <v>302</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>303</v>
       </c>
-      <c r="D21" s="29" t="s">
+      <c r="D21" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="E21" s="10" t="n">
+      <c r="E21" s="10">
         <v>3</v>
       </c>
-      <c r="F21" s="10" t="n">
+      <c r="F21" s="10">
         <v>1.5</v>
       </c>
-      <c r="G21" s="27" t="s">
+      <c r="G21" s="10" t="s">
         <v>61</v>
       </c>
       <c r="H21" s="9"/>
       <c r="I21" s="9"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="22" t="s">
         <v>304</v>
       </c>
@@ -5505,23 +5234,23 @@
       <c r="D22" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="E22" s="6">
         <v>3</v>
       </c>
-      <c r="F22" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" s="25" t="s">
+      <c r="F22" s="6">
+        <v>1</v>
+      </c>
+      <c r="G22" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="15" t="s">
         <v>305</v>
       </c>
-      <c r="B23" s="26" t="s">
+      <c r="B23" s="25" t="s">
         <v>104</v>
       </c>
       <c r="C23" s="9" t="s">
@@ -5530,19 +5259,19 @@
       <c r="D23" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E23" s="10" t="n">
+      <c r="E23" s="10">
         <v>3</v>
       </c>
-      <c r="F23" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="G23" s="27" t="s">
+      <c r="F23" s="10">
+        <v>2</v>
+      </c>
+      <c r="G23" s="10" t="s">
         <v>61</v>
       </c>
       <c r="H23" s="9"/>
       <c r="I23" s="9"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="22" t="s">
         <v>306</v>
       </c>
@@ -5555,75 +5284,66 @@
       <c r="D24" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="E24" s="6">
         <v>3</v>
       </c>
-      <c r="F24" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="25" t="s">
+      <c r="F24" s="6">
+        <v>1</v>
+      </c>
+      <c r="G24" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C26" s="30" t="s">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C26" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="F26" s="31" t="n">
-        <f aca="false">SUM(F2:F24)</f>
+      <c r="F26" s="29">
+        <f>SUM(F2:F24)</f>
         <v>26.5</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C27" s="30" t="s">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C27" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="F27" s="31" t="n">
-        <f aca="false">SUMIF(G2:G24,"Feito",F2:F24)</f>
+      <c r="F27" s="29">
+        <f>SUMIF(G2:G24,"Feito",F2:F24)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I24"/>
+  <autoFilter ref="A1:I24" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G2:G24" type="list">
+    <dataValidation type="list" allowBlank="1" sqref="G2:G24" xr:uid="{00000000-0002-0000-0500-000000000000}">
       <formula1>"Backlog,A Fazer,Fazendo,Em Review,Feito"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:I23"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="28"/>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="3" max="3" width="48" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="7" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>31</v>
       </c>
@@ -5652,7 +5372,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
         <v>308</v>
       </c>
@@ -5665,23 +5385,23 @@
       <c r="D2" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E2" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="6" t="n">
+      <c r="E2" s="6">
+        <v>1</v>
+      </c>
+      <c r="F2" s="6">
         <v>0.5</v>
       </c>
-      <c r="G2" s="25" t="s">
+      <c r="G2" s="6" t="s">
         <v>44</v>
       </c>
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
         <v>310</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="25" t="s">
         <v>309</v>
       </c>
       <c r="C3" s="9" t="s">
@@ -5690,19 +5410,19 @@
       <c r="D3" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E3" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="10" t="n">
+      <c r="E3" s="10">
+        <v>1</v>
+      </c>
+      <c r="F3" s="10">
         <v>1.5</v>
       </c>
-      <c r="G3" s="27" t="s">
+      <c r="G3" s="10" t="s">
         <v>44</v>
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="22" t="s">
         <v>311</v>
       </c>
@@ -5715,23 +5435,23 @@
       <c r="D4" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="6" t="n">
+      <c r="E4" s="6">
+        <v>1</v>
+      </c>
+      <c r="F4" s="6">
         <v>1.5</v>
       </c>
-      <c r="G4" s="25" t="s">
+      <c r="G4" s="6" t="s">
         <v>44</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
         <v>312</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="25" t="s">
         <v>313</v>
       </c>
       <c r="C5" s="9" t="s">
@@ -5740,19 +5460,19 @@
       <c r="D5" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E5" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="10" t="n">
+      <c r="E5" s="10">
+        <v>1</v>
+      </c>
+      <c r="F5" s="10">
         <v>0.5</v>
       </c>
-      <c r="G5" s="27" t="s">
+      <c r="G5" s="10" t="s">
         <v>44</v>
       </c>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="22" t="s">
         <v>315</v>
       </c>
@@ -5765,23 +5485,23 @@
       <c r="D6" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="25" t="s">
+      <c r="E6" s="6">
+        <v>1</v>
+      </c>
+      <c r="F6" s="6">
+        <v>1</v>
+      </c>
+      <c r="G6" s="6" t="s">
         <v>44</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
         <v>317</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="25" t="s">
         <v>318</v>
       </c>
       <c r="C7" s="9" t="s">
@@ -5790,19 +5510,19 @@
       <c r="D7" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" s="10" t="n">
+      <c r="E7" s="10">
+        <v>2</v>
+      </c>
+      <c r="F7" s="10">
         <v>0.5</v>
       </c>
-      <c r="G7" s="27" t="s">
+      <c r="G7" s="10" t="s">
         <v>61</v>
       </c>
       <c r="H7" s="9"/>
       <c r="I7" s="9"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="22" t="s">
         <v>320</v>
       </c>
@@ -5815,23 +5535,23 @@
       <c r="D8" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="25" t="s">
+      <c r="E8" s="6">
+        <v>2</v>
+      </c>
+      <c r="F8" s="6">
+        <v>1</v>
+      </c>
+      <c r="G8" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
         <v>322</v>
       </c>
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="25" t="s">
         <v>318</v>
       </c>
       <c r="C9" s="9" t="s">
@@ -5840,19 +5560,19 @@
       <c r="D9" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E9" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="27" t="s">
+      <c r="E9" s="10">
+        <v>2</v>
+      </c>
+      <c r="F9" s="10">
+        <v>1</v>
+      </c>
+      <c r="G9" s="10" t="s">
         <v>61</v>
       </c>
       <c r="H9" s="9"/>
       <c r="I9" s="9"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="22" t="s">
         <v>324</v>
       </c>
@@ -5865,23 +5585,23 @@
       <c r="D10" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="25" t="s">
+      <c r="E10" s="6">
+        <v>2</v>
+      </c>
+      <c r="F10" s="6">
+        <v>1</v>
+      </c>
+      <c r="G10" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
         <v>327</v>
       </c>
-      <c r="B11" s="26" t="s">
+      <c r="B11" s="25" t="s">
         <v>325</v>
       </c>
       <c r="C11" s="9" t="s">
@@ -5890,19 +5610,19 @@
       <c r="D11" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F11" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="27" t="s">
+      <c r="E11" s="10">
+        <v>2</v>
+      </c>
+      <c r="F11" s="10">
+        <v>1</v>
+      </c>
+      <c r="G11" s="10" t="s">
         <v>61</v>
       </c>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="22" t="s">
         <v>329</v>
       </c>
@@ -5915,23 +5635,23 @@
       <c r="D12" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="25" t="s">
+      <c r="E12" s="6">
+        <v>2</v>
+      </c>
+      <c r="F12" s="6">
+        <v>1</v>
+      </c>
+      <c r="G12" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
         <v>332</v>
       </c>
-      <c r="B13" s="26" t="s">
+      <c r="B13" s="25" t="s">
         <v>333</v>
       </c>
       <c r="C13" s="9" t="s">
@@ -5940,19 +5660,19 @@
       <c r="D13" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E13" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="27" t="s">
+      <c r="E13" s="10">
+        <v>2</v>
+      </c>
+      <c r="F13" s="10">
+        <v>1</v>
+      </c>
+      <c r="G13" s="10" t="s">
         <v>61</v>
       </c>
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="22" t="s">
         <v>335</v>
       </c>
@@ -5965,23 +5685,23 @@
       <c r="D14" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="25" t="s">
+      <c r="E14" s="6">
+        <v>2</v>
+      </c>
+      <c r="F14" s="6">
+        <v>1</v>
+      </c>
+      <c r="G14" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
         <v>337</v>
       </c>
-      <c r="B15" s="26" t="s">
+      <c r="B15" s="25" t="s">
         <v>338</v>
       </c>
       <c r="C15" s="9" t="s">
@@ -5990,19 +5710,19 @@
       <c r="D15" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F15" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="27" t="s">
+      <c r="E15" s="10">
+        <v>2</v>
+      </c>
+      <c r="F15" s="10">
+        <v>1</v>
+      </c>
+      <c r="G15" s="10" t="s">
         <v>61</v>
       </c>
       <c r="H15" s="9"/>
       <c r="I15" s="9"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="22" t="s">
         <v>340</v>
       </c>
@@ -6012,47 +5732,47 @@
       <c r="C16" s="5" t="s">
         <v>342</v>
       </c>
-      <c r="D16" s="28" t="s">
+      <c r="D16" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="E16" s="6">
         <v>3</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="F16" s="6">
         <v>1.5</v>
       </c>
-      <c r="G16" s="25" t="s">
+      <c r="G16" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
         <v>343</v>
       </c>
-      <c r="B17" s="26" t="s">
+      <c r="B17" s="25" t="s">
         <v>341</v>
       </c>
       <c r="C17" s="9" t="s">
         <v>344</v>
       </c>
-      <c r="D17" s="28" t="s">
+      <c r="D17" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="E17" s="10" t="n">
+      <c r="E17" s="10">
         <v>3</v>
       </c>
-      <c r="F17" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" s="27" t="s">
+      <c r="F17" s="10">
+        <v>1</v>
+      </c>
+      <c r="G17" s="10" t="s">
         <v>61</v>
       </c>
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="22" t="s">
         <v>345</v>
       </c>
@@ -6062,26 +5782,26 @@
       <c r="C18" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="D18" s="28" t="s">
+      <c r="D18" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="E18" s="6">
         <v>3</v>
       </c>
-      <c r="F18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="25" t="s">
+      <c r="F18" s="6">
+        <v>1</v>
+      </c>
+      <c r="G18" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="15" t="s">
         <v>348</v>
       </c>
-      <c r="B19" s="26" t="s">
+      <c r="B19" s="25" t="s">
         <v>104</v>
       </c>
       <c r="C19" s="9" t="s">
@@ -6090,19 +5810,19 @@
       <c r="D19" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="10" t="n">
+      <c r="E19" s="10">
         <v>3</v>
       </c>
-      <c r="F19" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" s="27" t="s">
+      <c r="F19" s="10">
+        <v>1</v>
+      </c>
+      <c r="G19" s="10" t="s">
         <v>61</v>
       </c>
       <c r="H19" s="9"/>
       <c r="I19" s="9"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="22" t="s">
         <v>349</v>
       </c>
@@ -6115,51 +5835,45 @@
       <c r="D20" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="E20" s="6">
         <v>3</v>
       </c>
-      <c r="F20" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G20" s="25" t="s">
+      <c r="F20" s="6">
+        <v>2</v>
+      </c>
+      <c r="G20" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C22" s="30" t="s">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C22" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="F22" s="31" t="n">
-        <f aca="false">SUM(F2:F20)</f>
+      <c r="F22" s="29">
+        <f>SUM(F2:F20)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C23" s="30" t="s">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C23" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="F23" s="31" t="n">
-        <f aca="false">SUMIF(G2:G20,"Feito",F2:F20)</f>
+      <c r="F23" s="29">
+        <f>SUMIF(G2:G20,"Feito",F2:F20)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I20"/>
+  <autoFilter ref="A1:I20" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G2:G20" type="list">
+    <dataValidation type="list" allowBlank="1" sqref="G2:G20" xr:uid="{00000000-0002-0000-0600-000000000000}">
       <formula1>"Backlog,A Fazer,Fazendo,Em Review,Feito"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>